--- a/output/20260814-live-003-线下活动核销结果.xlsx
+++ b/output/20260814-live-003-线下活动核销结果.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'堆头-逐店核验'!$A$3:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'堆头-销售检查'!$A$12:$H$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'堆头-照片文件检查'!$A$3:$I$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'堆头-异常补证'!$A$3:$F$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'堆头-异常补证'!$A$3:$F$12</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -97,7 +97,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -122,6 +122,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -157,7 +162,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -181,9 +186,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -194,6 +196,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -717,19 +725,19 @@
         <f>C5-E5</f>
         <v/>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>human_review</t>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>partial_pass</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>0/20家通过；20家补证</t>
+          <t>14/20家通过；6家补证</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>合同第1家“66广场家家欣”未通过：照片缺失、门店未匹配。；合同第2家“百佳华松岗店”未通过：照片缺失。；合同第3家“百佳华百货（公明店）”未通过：照片缺失。</t>
+          <t>合同第1家“66广场家家欣”未通过：门店未匹配。；合同第6家“金大福（东浦金正和总店）”未通过：期间未通过、门店未匹配、陈列标准未通过。；合同第10家“挺拇指生活超市（横沥店）”未通过：门店未匹配。</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -739,35 +747,35 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="10">
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9">
         <f>SUM(C4:C5)</f>
         <v/>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f>SUM(D4:D5)</f>
         <v/>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <f>SUM(E4:E5)</f>
         <v/>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <f>SUM(F4:F5)</f>
         <v/>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <f>IF(F6=0,"全部通过","存在暂挂/补证")</f>
         <v/>
       </c>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
-      <c r="J6" s="10" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:J6"/>
@@ -789,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -847,719 +855,285 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>合同第1家“66广场家家欣”未通过：照片缺失、门店未匹配。
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>合同第1家“66广场家家欣”未通过：门店未匹配。
 来源：核销资料-诚成26年4月【堆头20家】/堆头照片/1.厚街汉邦66广场家家欣.jpg</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>暂不支持该店1000.00元费用。</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>补充“66广场家家欣”与“厚街镇汉邦广场”的地址/入驻关系证明，或提供同日带完整门店名称与地点水印的现场照片。；补齐缺失原始照片文件</t>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>补充“66广场家家欣”与“厚街镇汉邦广场”的地址/入驻关系证明，或提供同日带完整门店名称与地点水印的现场照片。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>合同第2家“百佳华松岗店”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/2.松岗百佳华.jpg</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>合同第6家“金大福（东浦金正和总店）”未通过：期间未通过、门店未匹配、陈列标准未通过。
+来源：核销资料-诚成26年4月【堆头20家】/堆头照片/6.东浦金正和.jpg</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>暂不支持该店1000.00元费用。</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>如需严格同店证明，补充“百佳华松岗店”与“百佳华超市(松岗百佳华商场店)”的门店编码或地址映射。；补齐缺失原始照片文件</t>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>补充活动期内带可见日期、完整门店名称/地点水印的现场全景原图。；补充能清楚证明1平方米占地或至少4纵陈列的宽角度照片/尺寸标识。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>合同第3家“百佳华百货（公明店）”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/3.公明百佳华.jpg</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>合同第10家“挺拇指生活超市（横沥店）”未通过：门店未匹配。
+来源：核销资料-诚成26年4月【堆头20家】/堆头照片/10-1挺拇指生活超市(横沥店).jpg、核销资料-诚成26年4月【堆头20家】/堆头照片/10-2挺拇指生活超市(横沥店).jpg</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>暂不支持该店1000.00元费用。</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>补充公明店更名、门店编码或地址一致性证明。；补齐缺失原始照片文件</t>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>补充“挺拇指生活超市(横沥店)”位于或更名自“南铭购物乐园”的正式地址/门店映射，或提供带合同门店名称水印的现场照片。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>合同第4家“百佳华佳漾汇（新桥店）”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/4.新桥百佳华.jpg</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>合同第11家“人人购物广场荟和二店”未通过：门店未匹配。
+来源：核销资料-诚成26年4月【堆头20家】/堆头照片/11.人人购物荟和超市.jpg</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>暂不支持该店1000.00元费用。</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。；补齐缺失原始照片文件</t>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>补充“荟和二店”与“人人购物同乐店”的门店编码、地址或更名证明，或提供合同门店对应照片。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>合同第5家“华都超市（东坑大道北店）”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/5.华都超市(东坑大道北店).jpg</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>合同第14家“润家连锁超市（美联购物中心店）”未通过：门店未匹配。
+来源：核销资料-诚成26年4月【堆头20家】/堆头照片/14.润家连锁超市(美联购物中心店).jpg</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>暂不支持该店1000.00元费用。</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。；补齐缺失原始照片文件</t>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>提供“深圳紫云快捷宾馆”定位与润家连锁超市(美联购物中心店)同址的权威地址证明，或重拍带合同门店地点水印的现场照片。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>合同第6家“金大福（东浦金正和总店）”未通过：照片缺失、期间未通过、门店未匹配、陈列标准未通过。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/6.东浦金正和.jpg</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>合同第15家“百佳华（石岩店）”未通过：门店未匹配。
+来源：核销资料-诚成26年4月【堆头20家】/堆头照片/15。石岩百佳华.jpg</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>暂不支持该店1000.00元费用。</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>补充活动期内带可见日期、完整门店名称/地点水印的现场全景原图。；补充能清楚证明1平方米占地或至少4纵陈列的宽角度照片/尺寸标识。；补齐缺失原始照片文件</t>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>补充百佳华(石岩店)与“佳华豪苑”的权威地址/入驻关系证明，或提供带完整门店名地点水印的清晰原图。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>合同第7家“古原千禧（U·ONE 优城店）”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/7.宝安优城店.jpg</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>如需严格名称一致，补充U·ONE优城店与水印“古原千禧(优城店)”的门店编码或地址映射。；补齐缺失原始照片文件</t>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>PHOTO_ORIGINAL_METADATA_ABSENT</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>照片缺少可用的EXIF拍摄时间或GPS，主要依赖画面水印。</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>无法从原始文件元数据独立验证拍摄时空。</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>保留原始拍摄文件，或补充平台定位/签到记录。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>合同第8家“虎门家家欣”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/8.虎门赤岗家家欣.jpg</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>补充“虎门家家欣”与“赤岗家家欣商场”的地址、门店编码或组织关系证明。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>合同第9家“花都宜多”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/9.花都宜多.jpg</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>补充“花都宜多”与“炭步宜多百货”的门店编码或地址映射。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>合同第10家“挺拇指生活超市（横沥店）”未通过：照片缺失、门店未匹配。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/10-1挺拇指生活超市(横沥店).jpg、核销资料-诚成26年4月【堆头20家】/堆头照片/10-2挺拇指生活超市(横沥店).jpg</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>补充“挺拇指生活超市(横沥店)”位于或更名自“南铭购物乐园”的正式地址/门店映射，或提供带合同门店名称水印的现场照片。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>合同第11家“人人购物广场荟和二店”未通过：照片缺失、门店未匹配。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/11.人人购物荟和超市.jpg</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>补充“荟和二店”与“人人购物同乐店”的门店编码、地址或更名证明，或提供合同门店对应照片。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>合同第12家“三乐购物广场（森扬商业广场店）”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/12.三乐购物广场(森扬商业广场店).jpg</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>合同第13家“沙井九龙”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/13.沙井九龙.jpg</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>如需严格名称一致，补充“沙井九龙”与“九龙购物中心(宝安沙井店)”的门店编码或地址映射。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>合同第14家“润家连锁超市（美联购物中心店）”未通过：照片缺失、门店未匹配。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/14.润家连锁超市(美联购物中心店).jpg</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>提供“深圳紫云快捷宾馆”定位与润家连锁超市(美联购物中心店)同址的权威地址证明，或重拍带合同门店地点水印的现场照片。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>合同第15家“百佳华（石岩店）”未通过：照片缺失、门店未匹配。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/15。石岩百佳华.jpg</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>补充百佳华(石岩店)与“佳华豪苑”的权威地址/入驻关系证明，或提供带完整门店名地点水印的清晰原图。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>合同第16家“田心金正和”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/16.田心金正和.jpg</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>合同第17家“荟和超市（莹展荟店）”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/17·荟和超市(莹展荟店).jpg</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>合同第18家“三乐购物广场（坦洲店）”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/18.三乐购物广场(坦洲店).jpg</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>合同第19家“大康惠福源商业广场”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/19.福源大康惠.jpg</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>补充“大康惠福源商业广场”与“福源商业广场”的门店/地址映射。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>合同第20家“好多宝精选超市（龙眼市场店）”未通过：照片缺失。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/20.好多宝精选超市(龙眼市场店).jpg</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>补充好多宝精选超市(龙眼市场店)在“龙眼市场(龙眼路)”的门店编码、地址或入驻证明。；补齐缺失原始照片文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>PHOTO_ORIGINAL_METADATA_ABSENT</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>照片缺少可用的EXIF拍摄时间或GPS，主要依赖画面水印。</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>无法从原始文件元数据独立验证拍摄时空。</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>保留原始拍摄文件，或补充平台定位/签到记录。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>SALES_DATA_NOT_STORE_LEVEL</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>销售Excel为经销商汇总，不能拆分到合同中的各门店。
 来源：C:\Users\EDY\Desktop\新建文件夹\offline-activity-audit\input\.prepared\20260814-live-003\sources\promotional_display\核销资料-诚成26年4月【堆头20家】\2026年4月销售明细20260509164207765.xlsx</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>销售数据只能证明活动期总体销售，不能独立证明逐店执行。</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>如政策要求逐店销售佐证，补交门店级POS或出库明细。</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>SALES_EXCEL_EXTERNAL_LINKS</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>销售Excel有36个公式引用缺失的外部工作簿。
 来源：H10,H11,H16,H17,H21,H22,H27,H30,H31,H33,H34,H9,L11,L13,L14,L15,L16,L17,L2,L20</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>部分单位或零售价无法在当前文件内独立重算。</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>补交被引用主数据或将外链转为可追溯静态值。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F26"/>
+  <autoFilter ref="A3:F12"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -2444,58 +2018,58 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10">
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9">
         <f>SUM(F4:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <f>SUM(G4:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <f>SUM(H4:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="10" t="n"/>
-      <c r="J14" s="10">
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="9">
         <f>SUM(J4:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="9">
         <f>SUM(K4:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="9">
         <f>SUM(L4:L13)</f>
         <v/>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="9">
         <f>SUM(M4:M13)</f>
         <v/>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="9">
         <f>SUM(N4:N13)</f>
         <v/>
       </c>
-      <c r="O14" s="10" t="n"/>
-      <c r="P14" s="10">
+      <c r="O14" s="9" t="n"/>
+      <c r="P14" s="9">
         <f>SUM(P4:P13)</f>
         <v/>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="9">
         <f>SUM(Q4:Q13)</f>
         <v/>
       </c>
-      <c r="R14" s="10" t="n"/>
+      <c r="R14" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:R14"/>
@@ -5821,24 +5395,24 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="12" t="inlineStr">
+      <c r="A74" s="11" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B74" s="12" t="n"/>
-      <c r="C74" s="12" t="n"/>
-      <c r="D74" s="12" t="n"/>
-      <c r="E74" s="12" t="n"/>
-      <c r="F74" s="13">
+      <c r="B74" s="11" t="n"/>
+      <c r="C74" s="11" t="n"/>
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="11" t="n"/>
+      <c r="F74" s="12">
         <f>SUM(F4:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="12" t="n"/>
-      <c r="H74" s="12" t="n"/>
-      <c r="I74" s="12" t="n"/>
-      <c r="J74" s="12" t="n"/>
-      <c r="K74" s="13">
+      <c r="G74" s="11" t="n"/>
+      <c r="H74" s="11" t="n"/>
+      <c r="I74" s="11" t="n"/>
+      <c r="J74" s="11" t="n"/>
+      <c r="K74" s="12">
         <f>SUM(K4:K73)</f>
         <v/>
       </c>
@@ -6215,31 +5789,31 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="12">
         <f>SUM(B4:B10)</f>
         <v/>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="12">
         <f>SUM(C4:C10)</f>
         <v/>
       </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="13">
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="12">
         <f>SUM(E4:E10)</f>
         <v/>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <f>SUM(F4:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:I11"/>
@@ -7087,12 +6661,12 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>画面显示参半礼盒/牙膏在大型多层岛柜上多列陈列，可见至少4纵陈列特征。；水印地点与合同门店名称未形成独立一致映射。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=2bc5b681403c0d0e05ba6394449fd73b18e211370dbdfc3b1e3166678fb33aad，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/1.厚街汉邦66广场家家欣.jpg</t>
+          <t>画面显示参半礼盒/牙膏在大型多层岛柜上多列陈列，可见至少4纵陈列特征。；水印地点与合同门店名称未形成独立一致映射。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=2bc5b681403c0d0e05ba6394449fd73b18e211370dbdfc3b1e3166678fb33aad，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>补充“66广场家家欣”与“厚街镇汉邦广场”的地址/入驻关系证明，或提供同日带完整门店名称与地点水印的现场照片。；补齐缺失原始照片文件</t>
+          <t>补充“66广场家家欣”与“厚街镇汉邦广场”的地址/入驻关系证明，或提供同日带完整门店名称与地点水印的现场照片。</t>
         </is>
       </c>
     </row>
@@ -7143,9 +6717,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L5" s="6">
@@ -7154,12 +6728,12 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>参半产品在多层货架上形成多列陈列，可见至少4纵陈列特征。；合同简称与水印全称并非逐字相同。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=12b86e89b2996c4ee22ce55cfa65249237f10c2651963f0a74d6748f6fbdf29f，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/2.松岗百佳华.jpg</t>
+          <t>参半产品在多层货架上形成多列陈列，可见至少4纵陈列特征。；合同简称与水印全称并非逐字相同。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=12b86e89b2996c4ee22ce55cfa65249237f10c2651963f0a74d6748f6fbdf29f，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>如需严格同店证明，补充“百佳华松岗店”与“百佳华超市(松岗百佳华商场店)”的门店编码或地址映射。；补齐缺失原始照片文件</t>
+          <t>如需严格同店证明，补充“百佳华松岗店”与“百佳华超市(松岗百佳华商场店)”的门店编码或地址映射。</t>
         </is>
       </c>
     </row>
@@ -7210,9 +6784,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L6" s="6">
@@ -7221,12 +6795,12 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>多层端架上可见参半礼盒多列陈列，至少4个纵向陈列位可辨。；“百佳华百货”与“百佳华佳漾汇”的名称变化未附正式说明。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=334f7fe95b8f70a59cf89c0e2b65a47ba1a19c70d8b1695a51ecd59bdce07463，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/3.公明百佳华.jpg</t>
+          <t>多层端架上可见参半礼盒多列陈列，至少4个纵向陈列位可辨。；“百佳华百货”与“百佳华佳漾汇”的名称变化未附正式说明。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=334f7fe95b8f70a59cf89c0e2b65a47ba1a19c70d8b1695a51ecd59bdce07463，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>补充公明店更名、门店编码或地址一致性证明。；补齐缺失原始照片文件</t>
+          <t>补充公明店更名、门店编码或地址一致性证明。</t>
         </is>
       </c>
     </row>
@@ -7277,9 +6851,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L7" s="6">
@@ -7288,12 +6862,12 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>画面可见多层端架及参半礼盒/盒装产品多列陈列，满足至少4纵陈列的可见特征。；原图仅600×800，细节分辨率有限。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=df7c36d02303fc3b8df13e63888d0dcfed56860ca91d2a86501f67168d32c3ff，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/4.新桥百佳华.jpg</t>
+          <t>画面可见多层端架及参半礼盒/盒装产品多列陈列，满足至少4纵陈列的可见特征。；原图仅600×800，细节分辨率有限。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=df7c36d02303fc3b8df13e63888d0dcfed56860ca91d2a86501f67168d32c3ff，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。；补齐缺失原始照片文件</t>
+          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。</t>
         </is>
       </c>
     </row>
@@ -7344,9 +6918,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L8" s="6">
@@ -7355,12 +6929,12 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>画面可见参半产品在多层岛柜上成组、多列陈列，至少4纵陈列特征清晰。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=61e7f18669fe68e0686638d9bf53e6e488e8ce9ccb78192cdb6647915337dad0，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/5.华都超市(东坑大道北店).jpg</t>
+          <t>画面可见参半产品在多层岛柜上成组、多列陈列，至少4纵陈列特征清晰。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=61e7f18669fe68e0686638d9bf53e6e488e8ce9ccb78192cdb6647915337dad0，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。；补齐缺失原始照片文件</t>
+          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。</t>
         </is>
       </c>
     </row>
@@ -7414,12 +6988,12 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>画面可见参半3+2礼盒及竖盒放在红色促销台上，但单一正面角度无法可靠确认1平方米占地，且4纵陈列计数不够明确。；缺少任何画面内日期和门店/地点水印。；JPEG文件EXIF为空，无法从元数据独立验证拍摄日期或地点。；文件SHA-256=5443f87d47fe6646e5da357f0e53a41c8934f58255619fe749eae9b7ad9596a0，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/6.东浦金正和.jpg</t>
+          <t>画面可见参半3+2礼盒及竖盒放在红色促销台上，但单一正面角度无法可靠确认1平方米占地，且4纵陈列计数不够明确。；缺少任何画面内日期和门店/地点水印。；JPEG文件EXIF为空，无法从元数据独立验证拍摄日期或地点。；文件SHA-256=5443f87d47fe6646e5da357f0e53a41c8934f58255619fe749eae9b7ad9596a0，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>补充活动期内带可见日期、完整门店名称/地点水印的现场全景原图。；补充能清楚证明1平方米占地或至少4纵陈列的宽角度照片/尺寸标识。；补齐缺失原始照片文件</t>
+          <t>补充活动期内带可见日期、完整门店名称/地点水印的现场全景原图。；补充能清楚证明1平方米占地或至少4纵陈列的宽角度照片/尺寸标识。</t>
         </is>
       </c>
     </row>
@@ -7470,9 +7044,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L10" s="6">
@@ -7481,12 +7055,12 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>多层端架上参半礼盒/盒装产品有多列、多层陈列，可见至少4纵陈列特征。；水印省略合同中的“U·ONE”。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=80ff9c92a5eb1b780e9b0002a5d99c5239d71f592406992133c1e49e77e5834f，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/7.宝安优城店.jpg</t>
+          <t>多层端架上参半礼盒/盒装产品有多列、多层陈列，可见至少4纵陈列特征。；水印省略合同中的“U·ONE”。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=80ff9c92a5eb1b780e9b0002a5d99c5239d71f592406992133c1e49e77e5834f，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>如需严格名称一致，补充U·ONE优城店与水印“古原千禧(优城店)”的门店编码或地址映射。；补齐缺失原始照片文件</t>
+          <t>如需严格名称一致，补充U·ONE优城店与水印“古原千禧(优城店)”的门店编码或地址映射。</t>
         </is>
       </c>
     </row>
@@ -7537,9 +7111,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L11" s="6">
@@ -7548,12 +7122,12 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>多层端架上参半礼盒至少形成4个纵向陈列位。；原图仅600×800，且未提供赤岗与合同“虎门”分店的地址关系。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=a397af48c29cc108f54a66ac21d7aec414e79f20838ee3bb2e4851619d1f9e0a，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/8.虎门赤岗家家欣.jpg</t>
+          <t>多层端架上参半礼盒至少形成4个纵向陈列位。；原图仅600×800，且未提供赤岗与合同“虎门”分店的地址关系。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=a397af48c29cc108f54a66ac21d7aec414e79f20838ee3bb2e4851619d1f9e0a，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>补充“虎门家家欣”与“赤岗家家欣商场”的地址、门店编码或组织关系证明。；补齐缺失原始照片文件</t>
+          <t>补充“虎门家家欣”与“赤岗家家欣商场”的地址、门店编码或组织关系证明。</t>
         </is>
       </c>
     </row>
@@ -7604,9 +7178,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L12" s="6">
@@ -7615,12 +7189,12 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>画面为大型多面岛柜，参半牙膏、礼盒等产品多层多列陈列，可见面积/纵列明显超过最低特征。；合同简称未列“炭步”，未附门店编码。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=37a3bb4647855bff6147f370f02897142fb739c3b1f015546c9701327ca79c87，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/9.花都宜多.jpg</t>
+          <t>画面为大型多面岛柜，参半牙膏、礼盒等产品多层多列陈列，可见面积/纵列明显超过最低特征。；合同简称未列“炭步”，未附门店编码。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=37a3bb4647855bff6147f370f02897142fb739c3b1f015546c9701327ca79c87，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>补充“花都宜多”与“炭步宜多百货”的门店编码或地址映射。；补齐缺失原始照片文件</t>
+          <t>补充“花都宜多”与“炭步宜多百货”的门店编码或地址映射。</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7256,12 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>10-1为多层端架全景，10-2为另一侧近景；合并观察可见参半产品多层多列陈列，至少4纵陈列特征明确。；可见地点名称与合同门店名称不同，未提供商场入驻/更名映射。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；10-1挺拇指生活超市(横沥店).jpg SHA-256=f12dd735b31b0e3be209767b443a5dde76af047139821839e1c380befa2f17ba、精确哈希出现次数1；10-2挺拇指生活超市(横沥店).jpg SHA-256=1d4f8b92c71131ea2dbe09e06cff7496a82afca0ba4d7fced7ab272948670884、精确哈希出现次数1；两图内容不同，感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/10-1挺拇指生活超市(横沥店).jpg、核销资料-诚成26年4月【堆头20家】/堆头照片/10-2挺拇指生活超市(横沥店).jpg</t>
+          <t>10-1为多层端架全景，10-2为另一侧近景；合并观察可见参半产品多层多列陈列，至少4纵陈列特征明确。；可见地点名称与合同门店名称不同，未提供商场入驻/更名映射。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；10-1挺拇指生活超市(横沥店).jpg SHA-256=f12dd735b31b0e3be209767b443a5dde76af047139821839e1c380befa2f17ba、精确哈希出现次数1；10-2挺拇指生活超市(横沥店).jpg SHA-256=1d4f8b92c71131ea2dbe09e06cff7496a82afca0ba4d7fced7ab272948670884、精确哈希出现次数1；两图内容不同，感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>补充“挺拇指生活超市(横沥店)”位于或更名自“南铭购物乐园”的正式地址/门店映射，或提供带合同门店名称水印的现场照片。；补齐缺失原始照片文件</t>
+          <t>补充“挺拇指生活超市(横沥店)”位于或更名自“南铭购物乐园”的正式地址/门店映射，或提供带合同门店名称水印的现场照片。</t>
         </is>
       </c>
     </row>
@@ -7749,12 +7323,12 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>大型多层端架上参半产品有多列多层陈列，至少4纵陈列特征明确。；水印指向“同乐店”，合同指向“二店”。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=7cf34a44ba05a348179771b0c36be20c19f6a0a76fb0c72fc6742c1070011f87，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/11.人人购物荟和超市.jpg</t>
+          <t>大型多层端架上参半产品有多列多层陈列，至少4纵陈列特征明确。；水印指向“同乐店”，合同指向“二店”。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=7cf34a44ba05a348179771b0c36be20c19f6a0a76fb0c72fc6742c1070011f87，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>补充“荟和二店”与“人人购物同乐店”的门店编码、地址或更名证明，或提供合同门店对应照片。；补齐缺失原始照片文件</t>
+          <t>补充“荟和二店”与“人人购物同乐店”的门店编码、地址或更名证明，或提供合同门店对应照片。</t>
         </is>
       </c>
     </row>
@@ -7805,9 +7379,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L15" s="6">
@@ -7816,12 +7390,12 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>参半产品在宽幅多层陈列柜上多列摆放，上方另有堆叠，至少4纵陈列特征明确。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=817e1b01120475a5f72ab39bce2334a3f0c5d2d7c66d02b0d02e648e70bca0e9，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/12.三乐购物广场(森扬商业广场店).jpg</t>
+          <t>参半产品在宽幅多层陈列柜上多列摆放，上方另有堆叠，至少4纵陈列特征明确。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=817e1b01120475a5f72ab39bce2334a3f0c5d2d7c66d02b0d02e648e70bca0e9，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。；补齐缺失原始照片文件</t>
+          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。</t>
         </is>
       </c>
     </row>
@@ -7872,9 +7446,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L16" s="6">
@@ -7883,12 +7457,12 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>大型岛柜上参半牙膏多层多列陈列，可见面积及纵列均明显达到合同陈列特征。；合同为简称，未列完整购物中心名称。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=bea6157436ef7f0a45babca793b9fc67e06ac2beacd1b9eae36c44097b0e3888，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/13.沙井九龙.jpg</t>
+          <t>大型岛柜上参半牙膏多层多列陈列，可见面积及纵列均明显达到合同陈列特征。；合同为简称，未列完整购物中心名称。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=bea6157436ef7f0a45babca793b9fc67e06ac2beacd1b9eae36c44097b0e3888，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>如需严格名称一致，补充“沙井九龙”与“九龙购物中心(宝安沙井店)”的门店编码或地址映射。；补齐缺失原始照片文件</t>
+          <t>如需严格名称一致，补充“沙井九龙”与“九龙购物中心(宝安沙井店)”的门店编码或地址映射。</t>
         </is>
       </c>
     </row>
@@ -7950,12 +7524,12 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>画面中参半礼盒/牙膏在多层货架上形成多列陈列，至少4纵陈列特征明确。；可见地点指向宾馆，与合同门店名称冲突。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=0589b66788746499b68c9813b97ef042c2d1a239cd70be63056d57f4a9587fe5，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/14.润家连锁超市(美联购物中心店).jpg</t>
+          <t>画面中参半礼盒/牙膏在多层货架上形成多列陈列，至少4纵陈列特征明确。；可见地点指向宾馆，与合同门店名称冲突。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=0589b66788746499b68c9813b97ef042c2d1a239cd70be63056d57f4a9587fe5，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>提供“深圳紫云快捷宾馆”定位与润家连锁超市(美联购物中心店)同址的权威地址证明，或重拍带合同门店地点水印的现场照片。；补齐缺失原始照片文件</t>
+          <t>提供“深圳紫云快捷宾馆”定位与润家连锁超市(美联购物中心店)同址的权威地址证明，或重拍带合同门店地点水印的现场照片。</t>
         </is>
       </c>
     </row>
@@ -8017,12 +7591,12 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>虽画面略模糊，但多层端架上参半礼盒/盒装产品至少4纵陈列仍可辨。；可见地点是“佳华豪苑”，未提供其与百佳华石岩店同址的证据。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=9845f5c8c808e139ae93bf4a163372cf5e54e7aeb39a8dfbfa1d0aa47e5dfca8，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/15。石岩百佳华.jpg</t>
+          <t>虽画面略模糊，但多层端架上参半礼盒/盒装产品至少4纵陈列仍可辨。；可见地点是“佳华豪苑”，未提供其与百佳华石岩店同址的证据。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=9845f5c8c808e139ae93bf4a163372cf5e54e7aeb39a8dfbfa1d0aa47e5dfca8，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>补充百佳华(石岩店)与“佳华豪苑”的权威地址/入驻关系证明，或提供带完整门店名地点水印的清晰原图。；补齐缺失原始照片文件</t>
+          <t>补充百佳华(石岩店)与“佳华豪苑”的权威地址/入驻关系证明，或提供带完整门店名地点水印的清晰原图。</t>
         </is>
       </c>
     </row>
@@ -8073,9 +7647,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L19" s="6">
@@ -8084,12 +7658,12 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>大型多面岛柜上参半礼盒、牙膏等多层多列陈列，可见面积/纵列明显达到合同陈列特征。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=f00f97dc46a52568db5b292f7edb26bedfbc0d6f786e746acea6a56940a7c500，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/16.田心金正和.jpg</t>
+          <t>大型多面岛柜上参半礼盒、牙膏等多层多列陈列，可见面积/纵列明显达到合同陈列特征。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=f00f97dc46a52568db5b292f7edb26bedfbc0d6f786e746acea6a56940a7c500，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。；补齐缺失原始照片文件</t>
+          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。</t>
         </is>
       </c>
     </row>
@@ -8140,9 +7714,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L20" s="6">
@@ -8151,12 +7725,12 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>大型多面岛柜上参半盒装产品多层多列陈列，可见面积/纵列明显达到合同陈列特征。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=c6a9ac8b3b620adf996334ec432e725c45b4e302c481354caa4959a97c6f1ef1，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/17·荟和超市(莹展荟店).jpg</t>
+          <t>大型多面岛柜上参半盒装产品多层多列陈列，可见面积/纵列明显达到合同陈列特征。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=c6a9ac8b3b620adf996334ec432e725c45b4e302c481354caa4959a97c6f1ef1，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。；补齐缺失原始照片文件</t>
+          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。</t>
         </is>
       </c>
     </row>
@@ -8207,9 +7781,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L21" s="6">
@@ -8218,12 +7792,12 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>多层端架上参半礼盒成组陈列，画面下层可见至少4个纵向陈列位。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=61f0c8113bfbfafd9cc02a2ae69881cb8cc456e911c32c78ba618ab3467153fe，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/18.三乐购物广场(坦洲店).jpg</t>
+          <t>多层端架上参半礼盒成组陈列，画面下层可见至少4个纵向陈列位。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=61f0c8113bfbfafd9cc02a2ae69881cb8cc456e911c32c78ba618ab3467153fe，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。；补齐缺失原始照片文件</t>
+          <t>如制度要求原始定位证明，补充含EXIF/GPS的原始未压缩照片。</t>
         </is>
       </c>
     </row>
@@ -8274,9 +7848,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L22" s="6">
@@ -8285,12 +7859,12 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>大型四面岛柜上参半牙膏/礼盒多层多列陈列，可见面积与纵列明显达到合同陈列特征。；水印为缩略名称，未附正式门店名称映射。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=a83b7852588f47ff9fc8c43791eab025aa930eb7efa97d4da13cd54024be754c，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/19.福源大康惠.jpg</t>
+          <t>大型四面岛柜上参半牙膏/礼盒多层多列陈列，可见面积与纵列明显达到合同陈列特征。；水印为缩略名称，未附正式门店名称映射。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=a83b7852588f47ff9fc8c43791eab025aa930eb7efa97d4da13cd54024be754c，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>补充“大康惠福源商业广场”与“福源商业广场”的门店/地址映射。；补齐缺失原始照片文件</t>
+          <t>补充“大康惠福源商业广场”与“福源商业广场”的门店/地址映射。</t>
         </is>
       </c>
     </row>
@@ -8341,9 +7915,9 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>补证</t>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="L23" s="6">
@@ -8352,40 +7926,40 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>多层端架上参半盒装产品至少形成4个纵向陈列位。；水印只证明龙眼市场地点，未直接显示合同门店品牌。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=a2bc6e9f7833a6b2dace149843649c6c2a6b5988e04def5a9bc64d4b2b8740fc，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。；结构化核验引用了不存在的照片文件：核销资料-诚成26年4月【堆头20家】/堆头照片/20.好多宝精选超市(龙眼市场店).jpg</t>
+          <t>多层端架上参半盒装产品至少形成4个纵向陈列位。；水印只证明龙眼市场地点，未直接显示合同门店品牌。；JPEG文件EXIF为空；日期和地点只来自画面内可见水印，未由EXIF/GPS独立验证。；文件SHA-256=a2bc6e9f7833a6b2dace149843649c6c2a6b5988e04def5a9bc64d4b2b8740fc，在本案21张照片中精确哈希出现次数为1；感知指纹筛查未见近似重复。</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>补充好多宝精选超市(龙眼市场店)在“龙眼市场(龙眼路)”的门店编码、地址或入驻证明。；补齐缺失原始照片文件</t>
+          <t>补充好多宝精选超市(龙眼市场店)在“龙眼市场(龙眼路)”的门店编码、地址或入驻证明。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="13">
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="12">
         <f>SUM(D4:D23)</f>
         <v/>
       </c>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="13">
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="12">
         <f>SUM(L4:L23)</f>
         <v/>
       </c>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n"/>
+      <c r="M24" s="11" t="n"/>
+      <c r="N24" s="11" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:N24"/>
@@ -9897,21 +9471,21 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="12" t="n"/>
-      <c r="E49" s="12" t="n"/>
-      <c r="F49" s="12" t="n"/>
-      <c r="G49" s="13">
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="12">
         <f>SUM(G13:G48)</f>
         <v/>
       </c>
-      <c r="H49" s="13">
+      <c r="H49" s="12">
         <f>SUM(H13:H48)</f>
         <v/>
       </c>

--- a/output/20260814-live-003-线下活动核销结果.xlsx
+++ b/output/20260814-live-003-线下活动核销结果.xlsx
@@ -8,27 +8,36 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核销总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员激励-SKU逐项" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员激励-门店SKU明细" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员激励-门店转账" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员激励-转账凭证" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员激励-异常补证" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="堆头-逐店核验" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="堆头-销售检查" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="堆头-照片文件检查" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="堆头-异常补证" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型用量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核销步骤说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.4.1分析维度" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文件读取清单" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="堆头-逐店核验" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="堆头-销售检查" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="堆头-照片文件检查" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="堆头-异常补证" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员激励-SKU逐项" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员激励-门店SKU明细" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员激励-门店转账" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员激励-转账凭证" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员激励-图片文件检查" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员激励-异常补证" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'核销总览'!$A$3:$J$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'人员激励-SKU逐项'!$A$3:$R$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'人员激励-门店SKU明细'!$A$3:$K$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'人员激励-门店转账'!$A$3:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'人员激励-转账凭证'!$A$3:$I$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'人员激励-异常补证'!$A$3:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'堆头-逐店核验'!$A$3:$N$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'堆头-销售检查'!$A$12:$H$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'堆头-照片文件检查'!$A$3:$I$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'堆头-异常补证'!$A$3:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'核销总览'!$A$3:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'核销步骤说明'!$A$3:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'1.4.1分析维度'!$A$3:$K$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'文件读取清单'!$A$3:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'堆头-逐店核验'!$A$3:$N$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'堆头-销售检查'!$A$12:$H$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'堆头-照片文件检查'!$A$3:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'堆头-异常补证'!$A$3:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'人员激励-SKU逐项'!$A$3:$R$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'人员激励-门店SKU明细'!$A$3:$K$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'人员激励-门店转账'!$A$3:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'人员激励-转账凭证'!$A$3:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'人员激励-图片文件检查'!$A$3:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'人员激励-异常补证'!$A$3:$F$10</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -37,7 +46,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,11 +94,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00008000"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="10"/>
@@ -97,7 +101,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -116,11 +120,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
@@ -131,7 +130,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -160,7 +169,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,32 +185,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -571,32 +580,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="72" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="72" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 核销试审结果（详细证据链版）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
+          <t>线下活动核销结果：通过 / 异常 / 待补件汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数量与门店证据先逐项核验，再汇总金额；AI结论用于辅助复核，不替代最终审批。</t>
+          <t>先逐SKU、逐门店、逐转账核验，再汇总通过、异常、待补件和金额结论；最终外部交付仅此一份Excel，不保存运行日志。</t>
         </is>
       </c>
     </row>
@@ -613,46 +625,61 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>核验对象</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>异常</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>待补件</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>结算/申请金额</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>证据支持金额</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>建议通过金额</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>暂挂金额</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>AI结论</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>逐项核验覆盖</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>关键异常</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>汇总结论</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>关键原因</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>明细入口</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="72" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SQ202604300025-HX202605260014-郑州雨瑶-人员激励</t>
@@ -663,43 +690,58 @@
           <t>人员激励</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>10个结算SKU、7家门店转账</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>10个SKU数量/金额通过</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>7项异常提示（高0、中7）</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>7项待说明/补证</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>7350</v>
       </c>
-      <c r="D4" s="5">
+      <c r="H4" s="5">
         <f>MIN('人员激励-SKU逐项'!Q14,'人员激励-门店转账'!E11)</f>
         <v/>
       </c>
-      <c r="E4" s="6">
-        <f>MIN(C4,D4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="6">
-        <f>C4-E4</f>
-        <v/>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>conditional_pass</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>10/10个SKU数量匹配；70条门店SKU来源行</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="5">
+        <f>MIN(G4,H4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="5">
+        <f>G4-I4</f>
+        <v/>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>待补件（金额可通过）</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>结算单第1行SKU映射置信度为medium。；结算单第5行SKU映射置信度为medium。；结算单第9行SKU映射置信度为medium。</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>查看“人员激励-SKU逐项”</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="72" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】</t>
@@ -710,439 +752,106 @@
           <t>堆头陈列</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>20家合同门店</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>14家通过</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>9项异常提示（高6、中3）</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>6家待补件</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>20000</v>
       </c>
-      <c r="D5" s="5">
+      <c r="H5" s="5">
         <f>'堆头-逐店核验'!L24</f>
         <v/>
       </c>
-      <c r="E5" s="6">
-        <f>MIN(C5,D5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="6">
-        <f>C5-E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>partial_pass</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>14/20家通过；6家补证</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5">
+        <f>MIN(G5,H5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="5">
+        <f>G5-I5</f>
+        <v/>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>待补件</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>合同第1家“66广场家家欣”未通过：门店未匹配。；合同第6家“金大福（东浦金正和总店）”未通过：期间未通过、门店未匹配、陈列标准未通过。；合同第10家“挺拇指生活超市（横沥店）”未通过：门店未匹配。</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>查看“堆头-逐店核验”</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9">
-        <f>SUM(C4:C5)</f>
-        <v/>
-      </c>
-      <c r="D6" s="9">
-        <f>SUM(D4:D5)</f>
-        <v/>
-      </c>
-      <c r="E6" s="9">
-        <f>SUM(E4:E5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="9">
-        <f>SUM(F4:F5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="9">
-        <f>IF(F6=0,"全部通过","存在暂挂/补证")</f>
-        <v/>
-      </c>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8">
+        <f>SUM(G4:G5)</f>
+        <v/>
+      </c>
+      <c r="H6" s="8">
+        <f>SUM(H4:H5)</f>
+        <v/>
+      </c>
+      <c r="I6" s="8">
+        <f>SUM(I4:I5)</f>
+        <v/>
+      </c>
+      <c r="J6" s="8">
+        <f>SUM(J4:J5)</f>
+        <v/>
+      </c>
+      <c r="K6" s="8">
+        <f>IF(J6=0,"全部通过","存在异常/待补件")</f>
+        <v/>
+      </c>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J6"/>
+  <autoFilter ref="A3:M6"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】：异常与补证清单</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>高风险影响数量/金额或核心证据；中风险表示口径、身份或真实性证据仍需说明。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>异常代码</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>发现</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>影响</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>补证/处理建议</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>合同第1家“66广场家家欣”未通过：门店未匹配。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/1.厚街汉邦66广场家家欣.jpg</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>补充“66广场家家欣”与“厚街镇汉邦广场”的地址/入驻关系证明，或提供同日带完整门店名称与地点水印的现场照片。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>合同第6家“金大福（东浦金正和总店）”未通过：期间未通过、门店未匹配、陈列标准未通过。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/6.东浦金正和.jpg</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>补充活动期内带可见日期、完整门店名称/地点水印的现场全景原图。；补充能清楚证明1平方米占地或至少4纵陈列的宽角度照片/尺寸标识。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>合同第10家“挺拇指生活超市（横沥店）”未通过：门店未匹配。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/10-1挺拇指生活超市(横沥店).jpg、核销资料-诚成26年4月【堆头20家】/堆头照片/10-2挺拇指生活超市(横沥店).jpg</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>补充“挺拇指生活超市(横沥店)”位于或更名自“南铭购物乐园”的正式地址/门店映射，或提供带合同门店名称水印的现场照片。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>合同第11家“人人购物广场荟和二店”未通过：门店未匹配。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/11.人人购物荟和超市.jpg</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>补充“荟和二店”与“人人购物同乐店”的门店编码、地址或更名证明，或提供合同门店对应照片。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>合同第14家“润家连锁超市（美联购物中心店）”未通过：门店未匹配。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/14.润家连锁超市(美联购物中心店).jpg</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>提供“深圳紫云快捷宾馆”定位与润家连锁超市(美联购物中心店)同址的权威地址证明，或重拍带合同门店地点水印的现场照片。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>合同第15家“百佳华（石岩店）”未通过：门店未匹配。
-来源：核销资料-诚成26年4月【堆头20家】/堆头照片/15。石岩百佳华.jpg</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>暂不支持该店1000.00元费用。</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>补充百佳华(石岩店)与“佳华豪苑”的权威地址/入驻关系证明，或提供带完整门店名地点水印的清晰原图。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>PHOTO_ORIGINAL_METADATA_ABSENT</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>照片缺少可用的EXIF拍摄时间或GPS，主要依赖画面水印。</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>无法从原始文件元数据独立验证拍摄时空。</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>保留原始拍摄文件，或补充平台定位/签到记录。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>SALES_DATA_NOT_STORE_LEVEL</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>销售Excel为经销商汇总，不能拆分到合同中的各门店。
-来源：C:\Users\EDY\Desktop\新建文件夹\offline-activity-audit\input\.prepared\20260814-live-003\sources\promotional_display\核销资料-诚成26年4月【堆头20家】\2026年4月销售明细20260509164207765.xlsx</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>销售数据只能证明活动期总体销售，不能独立证明逐店执行。</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>如政策要求逐店销售佐证，补交门店级POS或出库明细。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>SALES_EXCEL_EXTERNAL_LINKS</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>销售Excel有36个公式引用缺失的外部工作簿。
-来源：H10,H11,H16,H17,H21,H22,H27,H30,H31,H33,H34,H9,L11,L13,L14,L15,L16,L17,L2,L20</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>部分单位或零售价无法在当前文件内独立重算。</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>补交被引用主数据或将外链转为可追溯静态值。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:F12"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1178,7 +887,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>先按结算行映射唯一条码，再汇总7家门店Excel来源行；数量、单价、行金额和支持金额分别计算。</t>
@@ -1307,41 +1016,41 @@
       <c r="G4" s="4" t="n">
         <v>238</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <f>IF(OR(F4="",G4=""),"",F4-G4)</f>
         <v/>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <f>IF(H4="","未匹配",IF(H4=0,"匹配","异常"))</f>
         <v/>
       </c>
       <c r="J4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <f>IF(F4="","",F4*J4)</f>
         <v/>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <f>G4*J4</f>
         <v/>
       </c>
       <c r="M4" s="4" t="n">
         <v>714</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="5">
         <f>M4-L4</f>
         <v/>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="5">
         <f>IF(N4=0,"匹配","异常")</f>
         <v/>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="5">
         <f>IF(OR(F4="",G4=""),0,MAX(0,MIN(F4,G4)))</f>
         <v/>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="5">
         <f>P4*J4</f>
         <v/>
       </c>
@@ -1381,41 +1090,41 @@
       <c r="G5" s="4" t="n">
         <v>275</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <f>IF(OR(F5="",G5=""),"",F5-G5)</f>
         <v/>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <f>IF(H5="","未匹配",IF(H5=0,"匹配","异常"))</f>
         <v/>
       </c>
       <c r="J5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <f>IF(F5="","",F5*J5)</f>
         <v/>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <f>G5*J5</f>
         <v/>
       </c>
       <c r="M5" s="4" t="n">
         <v>825</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="5">
         <f>M5-L5</f>
         <v/>
       </c>
-      <c r="O5" s="6">
+      <c r="O5" s="5">
         <f>IF(N5=0,"匹配","异常")</f>
         <v/>
       </c>
-      <c r="P5" s="6">
+      <c r="P5" s="5">
         <f>IF(OR(F5="",G5=""),0,MAX(0,MIN(F5,G5)))</f>
         <v/>
       </c>
-      <c r="Q5" s="6">
+      <c r="Q5" s="5">
         <f>P5*J5</f>
         <v/>
       </c>
@@ -1455,41 +1164,41 @@
       <c r="G6" s="4" t="n">
         <v>284</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <f>IF(OR(F6="",G6=""),"",F6-G6)</f>
         <v/>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <f>IF(H6="","未匹配",IF(H6=0,"匹配","异常"))</f>
         <v/>
       </c>
       <c r="J6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <f>IF(F6="","",F6*J6)</f>
         <v/>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <f>G6*J6</f>
         <v/>
       </c>
       <c r="M6" s="4" t="n">
         <v>852</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <f>M6-L6</f>
         <v/>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="5">
         <f>IF(N6=0,"匹配","异常")</f>
         <v/>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <f>IF(OR(F6="",G6=""),0,MAX(0,MIN(F6,G6)))</f>
         <v/>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="5">
         <f>P6*J6</f>
         <v/>
       </c>
@@ -1529,41 +1238,41 @@
       <c r="G7" s="4" t="n">
         <v>226</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <f>IF(OR(F7="",G7=""),"",F7-G7)</f>
         <v/>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <f>IF(H7="","未匹配",IF(H7=0,"匹配","异常"))</f>
         <v/>
       </c>
       <c r="J7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <f>IF(F7="","",F7*J7)</f>
         <v/>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <f>G7*J7</f>
         <v/>
       </c>
       <c r="M7" s="4" t="n">
         <v>678</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <f>M7-L7</f>
         <v/>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="5">
         <f>IF(N7=0,"匹配","异常")</f>
         <v/>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="5">
         <f>IF(OR(F7="",G7=""),0,MAX(0,MIN(F7,G7)))</f>
         <v/>
       </c>
-      <c r="Q7" s="6">
+      <c r="Q7" s="5">
         <f>P7*J7</f>
         <v/>
       </c>
@@ -1603,41 +1312,41 @@
       <c r="G8" s="4" t="n">
         <v>225</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <f>IF(OR(F8="",G8=""),"",F8-G8)</f>
         <v/>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <f>IF(H8="","未匹配",IF(H8=0,"匹配","异常"))</f>
         <v/>
       </c>
       <c r="J8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <f>IF(F8="","",F8*J8)</f>
         <v/>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <f>G8*J8</f>
         <v/>
       </c>
       <c r="M8" s="4" t="n">
         <v>675</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="5">
         <f>M8-L8</f>
         <v/>
       </c>
-      <c r="O8" s="6">
+      <c r="O8" s="5">
         <f>IF(N8=0,"匹配","异常")</f>
         <v/>
       </c>
-      <c r="P8" s="6">
+      <c r="P8" s="5">
         <f>IF(OR(F8="",G8=""),0,MAX(0,MIN(F8,G8)))</f>
         <v/>
       </c>
-      <c r="Q8" s="6">
+      <c r="Q8" s="5">
         <f>P8*J8</f>
         <v/>
       </c>
@@ -1677,41 +1386,41 @@
       <c r="G9" s="4" t="n">
         <v>252</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <f>IF(OR(F9="",G9=""),"",F9-G9)</f>
         <v/>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <f>IF(H9="","未匹配",IF(H9=0,"匹配","异常"))</f>
         <v/>
       </c>
       <c r="J9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <f>IF(F9="","",F9*J9)</f>
         <v/>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <f>G9*J9</f>
         <v/>
       </c>
       <c r="M9" s="4" t="n">
         <v>756</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <f>M9-L9</f>
         <v/>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="5">
         <f>IF(N9=0,"匹配","异常")</f>
         <v/>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="5">
         <f>IF(OR(F9="",G9=""),0,MAX(0,MIN(F9,G9)))</f>
         <v/>
       </c>
-      <c r="Q9" s="6">
+      <c r="Q9" s="5">
         <f>P9*J9</f>
         <v/>
       </c>
@@ -1751,41 +1460,41 @@
       <c r="G10" s="4" t="n">
         <v>239</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <f>IF(OR(F10="",G10=""),"",F10-G10)</f>
         <v/>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <f>IF(H10="","未匹配",IF(H10=0,"匹配","异常"))</f>
         <v/>
       </c>
       <c r="J10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <f>IF(F10="","",F10*J10)</f>
         <v/>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <f>G10*J10</f>
         <v/>
       </c>
       <c r="M10" s="4" t="n">
         <v>717</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="5">
         <f>M10-L10</f>
         <v/>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="5">
         <f>IF(N10=0,"匹配","异常")</f>
         <v/>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="5">
         <f>IF(OR(F10="",G10=""),0,MAX(0,MIN(F10,G10)))</f>
         <v/>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="5">
         <f>P10*J10</f>
         <v/>
       </c>
@@ -1825,41 +1534,41 @@
       <c r="G11" s="4" t="n">
         <v>278</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <f>IF(OR(F11="",G11=""),"",F11-G11)</f>
         <v/>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <f>IF(H11="","未匹配",IF(H11=0,"匹配","异常"))</f>
         <v/>
       </c>
       <c r="J11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <f>IF(F11="","",F11*J11)</f>
         <v/>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <f>G11*J11</f>
         <v/>
       </c>
       <c r="M11" s="4" t="n">
         <v>834</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="5">
         <f>M11-L11</f>
         <v/>
       </c>
-      <c r="O11" s="6">
+      <c r="O11" s="5">
         <f>IF(N11=0,"匹配","异常")</f>
         <v/>
       </c>
-      <c r="P11" s="6">
+      <c r="P11" s="5">
         <f>IF(OR(F11="",G11=""),0,MAX(0,MIN(F11,G11)))</f>
         <v/>
       </c>
-      <c r="Q11" s="6">
+      <c r="Q11" s="5">
         <f>P11*J11</f>
         <v/>
       </c>
@@ -1899,41 +1608,41 @@
       <c r="G12" s="4" t="n">
         <v>190</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <f>IF(OR(F12="",G12=""),"",F12-G12)</f>
         <v/>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <f>IF(H12="","未匹配",IF(H12=0,"匹配","异常"))</f>
         <v/>
       </c>
       <c r="J12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <f>IF(F12="","",F12*J12)</f>
         <v/>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <f>G12*J12</f>
         <v/>
       </c>
       <c r="M12" s="4" t="n">
         <v>570</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="5">
         <f>M12-L12</f>
         <v/>
       </c>
-      <c r="O12" s="6">
+      <c r="O12" s="5">
         <f>IF(N12=0,"匹配","异常")</f>
         <v/>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="5">
         <f>IF(OR(F12="",G12=""),0,MAX(0,MIN(F12,G12)))</f>
         <v/>
       </c>
-      <c r="Q12" s="6">
+      <c r="Q12" s="5">
         <f>P12*J12</f>
         <v/>
       </c>
@@ -1973,41 +1682,41 @@
       <c r="G13" s="4" t="n">
         <v>244</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <f>IF(OR(F13="",G13=""),"",F13-G13)</f>
         <v/>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <f>IF(H13="","未匹配",IF(H13=0,"匹配","异常"))</f>
         <v/>
       </c>
       <c r="J13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <f>IF(F13="","",F13*J13)</f>
         <v/>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <f>G13*J13</f>
         <v/>
       </c>
       <c r="M13" s="4" t="n">
         <v>732</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="5">
         <f>M13-L13</f>
         <v/>
       </c>
-      <c r="O13" s="6">
+      <c r="O13" s="5">
         <f>IF(N13=0,"匹配","异常")</f>
         <v/>
       </c>
-      <c r="P13" s="6">
+      <c r="P13" s="5">
         <f>IF(OR(F13="",G13=""),0,MAX(0,MIN(F13,G13)))</f>
         <v/>
       </c>
-      <c r="Q13" s="6">
+      <c r="Q13" s="5">
         <f>P13*J13</f>
         <v/>
       </c>
@@ -2018,58 +1727,58 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9">
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8">
         <f>SUM(F4:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <f>SUM(G4:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <f>SUM(H4:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9">
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8">
         <f>SUM(J4:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="8">
         <f>SUM(K4:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="8">
         <f>SUM(L4:L13)</f>
         <v/>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="8">
         <f>SUM(M4:M13)</f>
         <v/>
       </c>
-      <c r="N14" s="9">
+      <c r="N14" s="8">
         <f>SUM(N4:N13)</f>
         <v/>
       </c>
-      <c r="O14" s="9" t="n"/>
-      <c r="P14" s="9">
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8">
         <f>SUM(P4:P13)</f>
         <v/>
       </c>
-      <c r="Q14" s="9">
+      <c r="Q14" s="8">
         <f>SUM(Q4:Q13)</f>
         <v/>
       </c>
-      <c r="R14" s="9" t="n"/>
+      <c r="R14" s="8" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:R14"/>
@@ -2081,7 +1790,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2110,7 +1819,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>每一行均保留原Excel行号，并回指结算单行；这是SKU汇总数量的底层证据链。</t>
@@ -2215,7 +1924,7 @@
       <c r="J4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <f>IF(OR(F4="",J4=""),"",F4*J4)</f>
         <v/>
       </c>
@@ -2261,7 +1970,7 @@
       <c r="J5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <f>IF(OR(F5="",J5=""),"",F5*J5)</f>
         <v/>
       </c>
@@ -2307,7 +2016,7 @@
       <c r="J6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <f>IF(OR(F6="",J6=""),"",F6*J6)</f>
         <v/>
       </c>
@@ -2353,7 +2062,7 @@
       <c r="J7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <f>IF(OR(F7="",J7=""),"",F7*J7)</f>
         <v/>
       </c>
@@ -2399,7 +2108,7 @@
       <c r="J8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <f>IF(OR(F8="",J8=""),"",F8*J8)</f>
         <v/>
       </c>
@@ -2445,7 +2154,7 @@
       <c r="J9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <f>IF(OR(F9="",J9=""),"",F9*J9)</f>
         <v/>
       </c>
@@ -2491,7 +2200,7 @@
       <c r="J10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <f>IF(OR(F10="",J10=""),"",F10*J10)</f>
         <v/>
       </c>
@@ -2537,7 +2246,7 @@
       <c r="J11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <f>IF(OR(F11="",J11=""),"",F11*J11)</f>
         <v/>
       </c>
@@ -2583,7 +2292,7 @@
       <c r="J12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <f>IF(OR(F12="",J12=""),"",F12*J12)</f>
         <v/>
       </c>
@@ -2629,7 +2338,7 @@
       <c r="J13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <f>IF(OR(F13="",J13=""),"",F13*J13)</f>
         <v/>
       </c>
@@ -2675,7 +2384,7 @@
       <c r="J14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <f>IF(OR(F14="",J14=""),"",F14*J14)</f>
         <v/>
       </c>
@@ -2721,7 +2430,7 @@
       <c r="J15" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <f>IF(OR(F15="",J15=""),"",F15*J15)</f>
         <v/>
       </c>
@@ -2767,7 +2476,7 @@
       <c r="J16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <f>IF(OR(F16="",J16=""),"",F16*J16)</f>
         <v/>
       </c>
@@ -2813,7 +2522,7 @@
       <c r="J17" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <f>IF(OR(F17="",J17=""),"",F17*J17)</f>
         <v/>
       </c>
@@ -2859,7 +2568,7 @@
       <c r="J18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <f>IF(OR(F18="",J18=""),"",F18*J18)</f>
         <v/>
       </c>
@@ -2905,7 +2614,7 @@
       <c r="J19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <f>IF(OR(F19="",J19=""),"",F19*J19)</f>
         <v/>
       </c>
@@ -2951,7 +2660,7 @@
       <c r="J20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5">
         <f>IF(OR(F20="",J20=""),"",F20*J20)</f>
         <v/>
       </c>
@@ -2997,7 +2706,7 @@
       <c r="J21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <f>IF(OR(F21="",J21=""),"",F21*J21)</f>
         <v/>
       </c>
@@ -3043,7 +2752,7 @@
       <c r="J22" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="5">
         <f>IF(OR(F22="",J22=""),"",F22*J22)</f>
         <v/>
       </c>
@@ -3089,7 +2798,7 @@
       <c r="J23" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="5">
         <f>IF(OR(F23="",J23=""),"",F23*J23)</f>
         <v/>
       </c>
@@ -3135,7 +2844,7 @@
       <c r="J24" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="5">
         <f>IF(OR(F24="",J24=""),"",F24*J24)</f>
         <v/>
       </c>
@@ -3181,7 +2890,7 @@
       <c r="J25" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="5">
         <f>IF(OR(F25="",J25=""),"",F25*J25)</f>
         <v/>
       </c>
@@ -3227,7 +2936,7 @@
       <c r="J26" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="5">
         <f>IF(OR(F26="",J26=""),"",F26*J26)</f>
         <v/>
       </c>
@@ -3273,7 +2982,7 @@
       <c r="J27" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <f>IF(OR(F27="",J27=""),"",F27*J27)</f>
         <v/>
       </c>
@@ -3319,7 +3028,7 @@
       <c r="J28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <f>IF(OR(F28="",J28=""),"",F28*J28)</f>
         <v/>
       </c>
@@ -3365,7 +3074,7 @@
       <c r="J29" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5">
         <f>IF(OR(F29="",J29=""),"",F29*J29)</f>
         <v/>
       </c>
@@ -3411,7 +3120,7 @@
       <c r="J30" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <f>IF(OR(F30="",J30=""),"",F30*J30)</f>
         <v/>
       </c>
@@ -3457,7 +3166,7 @@
       <c r="J31" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="5">
         <f>IF(OR(F31="",J31=""),"",F31*J31)</f>
         <v/>
       </c>
@@ -3503,7 +3212,7 @@
       <c r="J32" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5">
         <f>IF(OR(F32="",J32=""),"",F32*J32)</f>
         <v/>
       </c>
@@ -3549,7 +3258,7 @@
       <c r="J33" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="5">
         <f>IF(OR(F33="",J33=""),"",F33*J33)</f>
         <v/>
       </c>
@@ -3595,7 +3304,7 @@
       <c r="J34" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="5">
         <f>IF(OR(F34="",J34=""),"",F34*J34)</f>
         <v/>
       </c>
@@ -3641,7 +3350,7 @@
       <c r="J35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="5">
         <f>IF(OR(F35="",J35=""),"",F35*J35)</f>
         <v/>
       </c>
@@ -3687,7 +3396,7 @@
       <c r="J36" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="5">
         <f>IF(OR(F36="",J36=""),"",F36*J36)</f>
         <v/>
       </c>
@@ -3733,7 +3442,7 @@
       <c r="J37" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="5">
         <f>IF(OR(F37="",J37=""),"",F37*J37)</f>
         <v/>
       </c>
@@ -3779,7 +3488,7 @@
       <c r="J38" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="5">
         <f>IF(OR(F38="",J38=""),"",F38*J38)</f>
         <v/>
       </c>
@@ -3825,7 +3534,7 @@
       <c r="J39" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="5">
         <f>IF(OR(F39="",J39=""),"",F39*J39)</f>
         <v/>
       </c>
@@ -3871,7 +3580,7 @@
       <c r="J40" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="5">
         <f>IF(OR(F40="",J40=""),"",F40*J40)</f>
         <v/>
       </c>
@@ -3917,7 +3626,7 @@
       <c r="J41" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="5">
         <f>IF(OR(F41="",J41=""),"",F41*J41)</f>
         <v/>
       </c>
@@ -3963,7 +3672,7 @@
       <c r="J42" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="5">
         <f>IF(OR(F42="",J42=""),"",F42*J42)</f>
         <v/>
       </c>
@@ -4009,7 +3718,7 @@
       <c r="J43" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K43" s="6">
+      <c r="K43" s="5">
         <f>IF(OR(F43="",J43=""),"",F43*J43)</f>
         <v/>
       </c>
@@ -4055,7 +3764,7 @@
       <c r="J44" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K44" s="6">
+      <c r="K44" s="5">
         <f>IF(OR(F44="",J44=""),"",F44*J44)</f>
         <v/>
       </c>
@@ -4101,7 +3810,7 @@
       <c r="J45" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K45" s="6">
+      <c r="K45" s="5">
         <f>IF(OR(F45="",J45=""),"",F45*J45)</f>
         <v/>
       </c>
@@ -4147,7 +3856,7 @@
       <c r="J46" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="5">
         <f>IF(OR(F46="",J46=""),"",F46*J46)</f>
         <v/>
       </c>
@@ -4193,7 +3902,7 @@
       <c r="J47" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="5">
         <f>IF(OR(F47="",J47=""),"",F47*J47)</f>
         <v/>
       </c>
@@ -4239,7 +3948,7 @@
       <c r="J48" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="5">
         <f>IF(OR(F48="",J48=""),"",F48*J48)</f>
         <v/>
       </c>
@@ -4285,7 +3994,7 @@
       <c r="J49" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K49" s="6">
+      <c r="K49" s="5">
         <f>IF(OR(F49="",J49=""),"",F49*J49)</f>
         <v/>
       </c>
@@ -4331,7 +4040,7 @@
       <c r="J50" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K50" s="6">
+      <c r="K50" s="5">
         <f>IF(OR(F50="",J50=""),"",F50*J50)</f>
         <v/>
       </c>
@@ -4377,7 +4086,7 @@
       <c r="J51" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K51" s="6">
+      <c r="K51" s="5">
         <f>IF(OR(F51="",J51=""),"",F51*J51)</f>
         <v/>
       </c>
@@ -4423,7 +4132,7 @@
       <c r="J52" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K52" s="6">
+      <c r="K52" s="5">
         <f>IF(OR(F52="",J52=""),"",F52*J52)</f>
         <v/>
       </c>
@@ -4469,7 +4178,7 @@
       <c r="J53" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K53" s="6">
+      <c r="K53" s="5">
         <f>IF(OR(F53="",J53=""),"",F53*J53)</f>
         <v/>
       </c>
@@ -4515,7 +4224,7 @@
       <c r="J54" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K54" s="6">
+      <c r="K54" s="5">
         <f>IF(OR(F54="",J54=""),"",F54*J54)</f>
         <v/>
       </c>
@@ -4561,7 +4270,7 @@
       <c r="J55" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K55" s="6">
+      <c r="K55" s="5">
         <f>IF(OR(F55="",J55=""),"",F55*J55)</f>
         <v/>
       </c>
@@ -4607,7 +4316,7 @@
       <c r="J56" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K56" s="6">
+      <c r="K56" s="5">
         <f>IF(OR(F56="",J56=""),"",F56*J56)</f>
         <v/>
       </c>
@@ -4653,7 +4362,7 @@
       <c r="J57" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K57" s="6">
+      <c r="K57" s="5">
         <f>IF(OR(F57="",J57=""),"",F57*J57)</f>
         <v/>
       </c>
@@ -4699,7 +4408,7 @@
       <c r="J58" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K58" s="6">
+      <c r="K58" s="5">
         <f>IF(OR(F58="",J58=""),"",F58*J58)</f>
         <v/>
       </c>
@@ -4745,7 +4454,7 @@
       <c r="J59" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K59" s="6">
+      <c r="K59" s="5">
         <f>IF(OR(F59="",J59=""),"",F59*J59)</f>
         <v/>
       </c>
@@ -4791,7 +4500,7 @@
       <c r="J60" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K60" s="6">
+      <c r="K60" s="5">
         <f>IF(OR(F60="",J60=""),"",F60*J60)</f>
         <v/>
       </c>
@@ -4837,7 +4546,7 @@
       <c r="J61" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K61" s="6">
+      <c r="K61" s="5">
         <f>IF(OR(F61="",J61=""),"",F61*J61)</f>
         <v/>
       </c>
@@ -4883,7 +4592,7 @@
       <c r="J62" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K62" s="6">
+      <c r="K62" s="5">
         <f>IF(OR(F62="",J62=""),"",F62*J62)</f>
         <v/>
       </c>
@@ -4929,7 +4638,7 @@
       <c r="J63" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K63" s="6">
+      <c r="K63" s="5">
         <f>IF(OR(F63="",J63=""),"",F63*J63)</f>
         <v/>
       </c>
@@ -4975,7 +4684,7 @@
       <c r="J64" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K64" s="6">
+      <c r="K64" s="5">
         <f>IF(OR(F64="",J64=""),"",F64*J64)</f>
         <v/>
       </c>
@@ -5021,7 +4730,7 @@
       <c r="J65" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K65" s="6">
+      <c r="K65" s="5">
         <f>IF(OR(F65="",J65=""),"",F65*J65)</f>
         <v/>
       </c>
@@ -5067,7 +4776,7 @@
       <c r="J66" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K66" s="6">
+      <c r="K66" s="5">
         <f>IF(OR(F66="",J66=""),"",F66*J66)</f>
         <v/>
       </c>
@@ -5113,7 +4822,7 @@
       <c r="J67" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K67" s="6">
+      <c r="K67" s="5">
         <f>IF(OR(F67="",J67=""),"",F67*J67)</f>
         <v/>
       </c>
@@ -5159,7 +4868,7 @@
       <c r="J68" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K68" s="6">
+      <c r="K68" s="5">
         <f>IF(OR(F68="",J68=""),"",F68*J68)</f>
         <v/>
       </c>
@@ -5205,7 +4914,7 @@
       <c r="J69" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K69" s="6">
+      <c r="K69" s="5">
         <f>IF(OR(F69="",J69=""),"",F69*J69)</f>
         <v/>
       </c>
@@ -5251,7 +4960,7 @@
       <c r="J70" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K70" s="6">
+      <c r="K70" s="5">
         <f>IF(OR(F70="",J70=""),"",F70*J70)</f>
         <v/>
       </c>
@@ -5297,7 +5006,7 @@
       <c r="J71" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K71" s="6">
+      <c r="K71" s="5">
         <f>IF(OR(F71="",J71=""),"",F71*J71)</f>
         <v/>
       </c>
@@ -5343,7 +5052,7 @@
       <c r="J72" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K72" s="6">
+      <c r="K72" s="5">
         <f>IF(OR(F72="",J72=""),"",F72*J72)</f>
         <v/>
       </c>
@@ -5389,7 +5098,7 @@
       <c r="J73" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K73" s="6">
+      <c r="K73" s="5">
         <f>IF(OR(F73="",J73=""),"",F73*J73)</f>
         <v/>
       </c>
@@ -5427,7 +5136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5454,7 +5163,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>金额集合一致不等于收款身份一致；截图未显示门店/收款人时单独标记为身份未验证。</t>
@@ -5528,7 +5237,7 @@
       <c r="E4" s="4" t="n">
         <v>1035</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <f>IF(OR(C4="",E4=""),"",E4-C4)</f>
         <v/>
       </c>
@@ -5568,7 +5277,7 @@
       <c r="E5" s="4" t="n">
         <v>1056</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <f>IF(OR(C5="",E5=""),"",E5-C5)</f>
         <v/>
       </c>
@@ -5608,7 +5317,7 @@
       <c r="E6" s="4" t="n">
         <v>1032</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <f>IF(OR(C6="",E6=""),"",E6-C6)</f>
         <v/>
       </c>
@@ -5648,7 +5357,7 @@
       <c r="E7" s="4" t="n">
         <v>1014</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <f>IF(OR(C7="",E7=""),"",E7-C7)</f>
         <v/>
       </c>
@@ -5688,7 +5397,7 @@
       <c r="E8" s="4" t="n">
         <v>1095</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <f>IF(OR(C8="",E8=""),"",E8-C8)</f>
         <v/>
       </c>
@@ -5728,7 +5437,7 @@
       <c r="E9" s="4" t="n">
         <v>1095</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <f>IF(OR(C9="",E9=""),"",E9-C9)</f>
         <v/>
       </c>
@@ -5768,7 +5477,7 @@
       <c r="E10" s="4" t="n">
         <v>1026</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <f>IF(OR(C10="",E10=""),"",E10-C10)</f>
         <v/>
       </c>
@@ -5825,7 +5534,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5852,7 +5561,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>同一笔转账的发送方与接收方气泡合并为一个transfer_id，同时保留画面出现次数。</t>
@@ -6205,7 +5914,242 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="68" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>人员激励：结算单与转账截图真实性风险辅助信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256检查完全重复，pHash筛查近似画面，dHash作为辅助；两张转账截图可能因同一聊天内容重叠而成为近似候选，需结合transfer_id去重，不能仅凭pHash判定造假。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>文件名</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>尺寸</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>大小(字节)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>SHA-256</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>pHash</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>dHash</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>EXIF时间</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>pHash候选</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>郑州雨瑶5.1-5.20人员激励活动结算单.jpg</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>最终结算单</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>645182</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>898a8061a91af8d681ccdb650b43a07a42b96272407ba249dd64dc53b4bbc4e6</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>d5f1828fc49e9332</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>84a9a99f93a6aeba</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>雨瑶人员激励红包图片.jpg</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>转账截图</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>1280×2774</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>194094</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>8aeda7f356dcf9123086cb55e6e60b4fc2049bfeaf784513dffcffa6f15b2529</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>872ef460ead5ea41</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>c884e470f9f1e969</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>雨瑶人员激励红包图片2.jpg（距离6）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>雨瑶人员激励红包图片2.jpg</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>转账截图</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1280×2774</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>192057</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>de4aa8f6d75027e207571fcf365ed5d805a350ff7622b45f29bc7d803db8c8ca</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>870ef568ea55aa51</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>c4c4e470f9f9e949</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>雨瑶人员激励红包图片.jpg（距离6）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6229,7 +6173,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>高风险影响数量/金额或核心证据；中风险表示口径、身份或真实性证据仍需说明。</t>
@@ -6269,214 +6213,214 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>NON_HIGH_CONFIDENCE_SKU_MAPPING</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>结算单第1行SKU映射置信度为medium。
 来源：settlement line 1</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>逐项数量虽然可计算，但商品身份仍有不确定性。</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>补充结算单条码或商品主数据映射。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>NON_HIGH_CONFIDENCE_SKU_MAPPING</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>结算单第5行SKU映射置信度为medium。
 来源：settlement line 5</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>逐项数量虽然可计算，但商品身份仍有不确定性。</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>补充结算单条码或商品主数据映射。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>NON_HIGH_CONFIDENCE_SKU_MAPPING</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>结算单第9行SKU映射置信度为medium。
 来源：settlement line 9</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>逐项数量虽然可计算，但商品身份仍有不确定性。</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>补充结算单条码或商品主数据映射。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>NON_HIGH_CONFIDENCE_SKU_MAPPING</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>结算单第10行SKU映射置信度为medium。
 来源：settlement line 10</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>逐项数量虽然可计算，但商品身份仍有不确定性。</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>补充结算单条码或商品主数据映射。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>CLAIM_DIFFERS_FROM_SETTLEMENT_LINES</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>实际核销金额7350.00与结算单逐行合计7353.00相差-3.00元。</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>需要明确人工调整、舍尾或扣减口径。</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>提供差额说明并在审批记录中保留调整依据。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>TRANSFER_STORE_IDENTITY_NOT_VISIBLE</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>转账截图未显示可核验的门店/收款人身份，只能按金额集合勾稽。</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>无法证明每笔款项实际支付给对应门店。</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>补充显示收款人、门店映射和交易单号的转账详情。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>TRANSFER_DATE_NOT_VISIBLE</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>转账截图未显示完整交易日期。</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>无法独立确认付款发生在活动结算周期内。</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>补充带交易日期和交易单号的明细。</t>
         </is>
@@ -6492,7 +6436,3599 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>模型调用量、失败重试与报价功能范围</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>只保存结构化用量统计，不保存模型事件流或stdout/stderr日志。报价表中的“工作量（人天）/报价”不是调用次数或Token预算；实际调用量取自模型执行返回的usage字段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>案件</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>调用次数</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>成功次数</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>失败次数</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>重试次数</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>输入Token</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>缓存输入Token</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>输出Token</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>推理输出Token</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>总Token(输入+输出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>3102566</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>2838400</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>37643</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>15886</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>3140209</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>SQ202604300025-HX202605260014-郑州雨瑶-人员激励</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1070616</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>973312</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>31944</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>16814</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>1102560</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8">
+        <f>SUM(D4:D5)</f>
+        <v/>
+      </c>
+      <c r="E6" s="8">
+        <f>SUM(E4:E5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="8">
+        <f>SUM(F4:F5)</f>
+        <v/>
+      </c>
+      <c r="G6" s="8">
+        <f>SUM(G4:G5)</f>
+        <v/>
+      </c>
+      <c r="H6" s="8">
+        <f>SUM(H4:H5)</f>
+        <v/>
+      </c>
+      <c r="I6" s="8">
+        <f>SUM(I4:I5)</f>
+        <v/>
+      </c>
+      <c r="J6" s="8">
+        <f>SUM(J4:J5)</f>
+        <v/>
+      </c>
+      <c r="K6" s="8">
+        <f>SUM(K4:K5)</f>
+        <v/>
+      </c>
+      <c r="L6" s="8">
+        <f>SUM(L4:L5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>案件</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>尝试序号</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>退出码</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>失败原因摘要</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>输入Token</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>缓存输入Token</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>输出Token</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>推理输出Token</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>总Token</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n">
+        <v>3102566</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>2838400</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>37643</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>15886</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>3140209</v>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>SQ202604300025-HX202605260014-郑州雨瑶-人员激励</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n">
+        <v>1070616</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>973312</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>31944</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>16814</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>1102560</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>报价功能项</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>工作量(人天)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>报价(元)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>原报价备注</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>本项目落点</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>文件分类与图像预处理</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>完成收件、分析、待复核、驳回、完成通知及群状态调整</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>主Skill安全解压、文件分类、图片/PDF/Excel读取预处理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>照片真实性风险辅助检测</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>读取EXIF/GPS/水印并进行pHash重复和跨活动复用检测</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>堆头子Skill读取EXIF/GPS/水印并做SHA-256/dHash同包去重；跨活动历史库未接入时明确标注未验证。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>现场/陈列照片多模态识别</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>10500</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>按固定活动规则识别门店、商品、排面、物料、位置和照片质量</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>堆头子Skill逐合同门店识别日期、地点、商品陈列、范围和质量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>发票及票据OCR结构化</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>提取发票代码、号码、金额、日期、购销方等关键字段</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>当前两个样例包无发票，状态为本案未触发；以后有发票时按字段结构化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>合同、费用明细及规则抽取</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>抽取合同金额、活动周期、Excel费用明细和核销政策字段</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>读取堆头合同、两个销售Excel、人员结算单和活动规则字段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>跨材料一致性与规则判断</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>对照片、票据、费用、预算、合同和门店信息进行字段及计算比对</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>人员激励逐SKU/转账，堆头逐门店，并执行1.4.1七维分析。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>结果汇总、异常重试与用量日志</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>汇总通过/异常/待补件结论，处理失败重试并记录模型调用量</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>汇总通过/异常/待补件；模型提取失败最多3次；只统计调用数和Token，不保存原始日志。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>小计</t>
+        </is>
+      </c>
+      <c r="B20" s="8">
+        <f>SUM(B13:B19)</f>
+        <v/>
+      </c>
+      <c r="C20" s="8">
+        <f>SUM(C13:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>核销步骤说明：每一步读什么文件、取什么数据、怎样比对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>建议按本页从上到下阅读，再点击最后一列进入底层明细。最终外部交付只有这一份Excel，不保存运行日志。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>步骤</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>读取文件</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>读取位置/字段</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>处理动作</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>比对对象</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>本步结果</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>结论/限制</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>明细入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>主流程</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SQ202604300025-HX202605260014-郑州雨瑶-人员激励.zip；SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>两个ZIP及全部压缩包成员</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>安全校验、解压、计算ZIP/文件SHA-256，并按文件组合路由到两个子Skill。</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>必须恰好1个人员激励包+1个堆头包</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>人员激励4个文件；堆头23个文件。</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>哈希固定收到后的文件身份，不等于真伪证明。</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>文件读取清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="96" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>雨瑶人员激励参半销售数据2.xlsx</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>工作表Sheet1，表头第1行；原Excel第2至83行中的有效行；字段为期间、门店、条码、商品、数量、单价、金额。</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>跳过空白/小计/合计，保留每条有效记录的原Excel行号，再按条码和门店汇总。</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>销售Excel自身明细与汇总</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>取得70条明细、7家门店、10个SKU、总数量2451。</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>这是结算数量的底层来源，不先看总金额。</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>人员激励-门店SKU明细</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="96" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>郑州雨瑶5.1-5.20人员激励活动结算单.jpg</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>最终结算单原图；逐行读取奖励单品、销售数量、奖励单价、奖励金额，以及总数量/总额/实际申报。</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>把结算单每一行作为独立待核对象；不把总额相等当作逐行通过。</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>最终结算单10行</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>取得10条结算SKU、结算数量2451、行奖励合计7353元、申报7350元。</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>结算单无条码时，商品名称映射必须保留依据和置信度。</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>人员激励-SKU逐项</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>销售Excel + 最终结算单</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>结算单每行 ↔ Excel唯一条码及其全部来源行</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>先做商品1:1映射，再把7家门店同一条码的数量相加；逐SKU比较Excel数量与结算数量，并计算数量×奖励单价。</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>10条结算SKU与10个Excel条码</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>10/10个SKU数量匹配；Excel 2451=2451结算数量；奖励计算7353元。</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>4个名称映射为中置信度，仍需商品条码/主数据补证；数量事实已逐行展示。</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>人员激励-SKU逐项</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="96" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>全部转账截图</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>每个金额气泡、方向、身份、日期和重复画面关系</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>把同一笔发送/接收镜像合并为一个transfer_id，再将7家门店应付金额集合与7笔转账金额集合比较。</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>门店应付 ↔ 去重转账</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>去重转账7笔、合计7353元，与结算行奖励合计一致。</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>金额一致不证明收款门店身份或转账日期；当前两项不可见。</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>人员激励-门店转账</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>诚成4月堆头陈列-经销商签订促销合同.pdf</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>合同逐页；读取客户、活动期、陈列标准、单店费用、申报金额和编号1—20门店。</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>建立20行合同门店基准，任何照片都必须回绑某一合同原始序号。</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>合同条款 ↔ 申报/照片</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>合同4页，20家×1000元=20000元。</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>合同是逐店判定基准；文件名只能帮助归组，不能证明地点。</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>堆头-逐店核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026年4月销售明细20260509164207765.xlsx</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>工作表Sheet1，表头第1行；读取客户、期间、商品编码、条码、商品、数量、零售价和金额。</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>直接读取公式和缓存值，汇总数量/金额并判断数据粒度。</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>销售期间/客户 ↔ 合同；销售数据粒度 ↔ 逐店执行要求</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>36条SKU，数量13744，零售金额352032；仅经销商汇总，无门店字段。</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>只能支持活动总体销售，不能证明20家逐店陈列。</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>堆头-销售检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片21张</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>每张原图的画面日期、地点/门店水印、陈列范围、清晰度；SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>逐张查重并绑定合同门店；每家分别判断照片、期间、门店、陈列、重复5项控制。</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>21张照片 ↔ 合同20家门店</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>14家通过，6家补证，支持14000元、暂挂6000元。</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>全部照片无可用EXIF/GPS；6家具体不一致见逐店明细。</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>堆头-逐店核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="96" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>主流程</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>两个ZIP内全部材料</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>方案1.4.1规定的真实性3项、合规性4项</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>对两个场景分别写明实际检查、状态、依据、能力边界和补证；缺证不默认为通过。</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>七维标准 ↔ 本次可得证据</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>形成14行（7维×2场景）分析矩阵。</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>SHA/dHash、EXIF、水印、预算、发票和合同各自有独立边界。</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>1.4.1分析维度</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="96" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>主流程</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>上述全部核验结果</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>逐SKU、逐门店、逐转账、七维分析及异常补证</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>先取证据支持金额，再与申报金额比较，合并成唯一Excel交付。</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>人员激励与堆头结果</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>人员激励建议通过7350元、暂挂0元；堆头建议通过14000元、暂挂6000元。</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>最终金额可追溯到本工作簿各明细页；不输出日志。</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>核销总览</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:I13"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId8"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="68" customWidth="1" min="9" max="9"/>
+    <col width="68" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>1.4.1 分析维度：真实性验证 + 合规性审查</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>逐场景覆盖方案规定的7项控制。状态说明：通过=关键证据完整；部分通过=部分对象未通过；部分验证=技术能力或证据不完整；证据不足=适用但缺证；本案未触发=本场景未提交该类材料且未规定为必交。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>分析维度</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>检测内容</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>1.4.1判定标准</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>本次读取文件/证据</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>实际执行的检查</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>本次判定依据</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>能力边界/补证要求</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>关联明细页</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>真实性验证</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>文件是否被篡改/伪造</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>EXIF信息完整性、图像指纹比对、水印一致性、数字签名验证</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>雨瑶人员激励参半销售数据2.xlsx；郑州雨瑶5.1-5.20人员激励活动结算单.jpg；转账截图2张</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>固定全部源文件SHA-256；读取结算单和转账截图可见内容；核对Excel公式与数值。</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>本包4个源文件已固定哈希；3张图片中EXIF时间0张、GPS 0张；但未提供数字签名、可信时间戳或像素级篡改检测结果。</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>SHA-256只证明收到后的字节身份，不能证明提交前从未被修改；需原始文件、数字签名或专业取证结果。</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>人员激励-图片文件检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="96" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>真实性验证</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>文件是否被篡改/伪造</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>EXIF信息完整性、图像指纹比对、水印一致性、数字签名验证</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>诚成4月堆头陈列-经销商签订促销合同.pdf；2026年4月销售明细20260509164207765.xlsx；现场照片21张</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>固定源文件SHA-256；对照片计算dHash；读取EXIF、画面日期地点水印，并逐店检查水印与合同门店的一致性。</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>部分验证</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>21张照片中EXIF时间0张、GPS 0张；完全重复组0、pHash近似候选0组。未提供数字签名或像素级篡改鉴定。</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>画面水印是可见线索，不是独立可信定位；哈希不能证明提交前未修改。需原始照片、可信时间/GPS或专业取证。</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>堆头-照片文件检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="96" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>真实性验证</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>照片是否为现场实拍</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>GPS坐标与申报门店匹配、拍摄时间在活动周期内、设备信息一致</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>本场景没有现场陈列照片；结算单和转账截图</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>检查转账截图中的身份、日期等可见字段，不把文件名或金额当作现场证明。</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>本案未触发</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>7笔去重转账中，身份可见4笔、日期可见0笔；材料不是门店现场实拍照片。</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>若人员激励制度要求现场执行照片，应另行提交带可信时间、地点和设备信息的原始照片。</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>人员激励-转账凭证</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>真实性验证</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>照片是否为现场实拍</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>GPS坐标与申报门店匹配、拍摄时间在活动周期内、设备信息一致</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>合同20家门店与21张现场照片</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>逐店读取画面可见日期和地点，比较活动期间、合同门店名称/地点及陈列标准；不从文件名推断日期或GPS。</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>部分通过</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>活动期匹配19/20家，门店地点匹配或兼容14/20家，陈列可确认19/20家；综合14/20家通过、6家补证。GPS与设备信息均不可用。</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>6家存在日期、地点或陈列证据缺口；需原始照片、可信定位/时间或正式门店地址映射。</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>堆头-逐店核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="96" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>真实性验证</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>文件是否重复使用</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>感知哈希（pHash）去重、跨活动文件复用检测</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>雨瑶人员激励参半销售数据2.xlsx；郑州雨瑶5.1-5.20人员激励活动结算单.jpg；转账截图2张</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>比较图片SHA-256并计算pHash近似指纹；按转账事件合并同一笔的发送/接收画面。</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>部分验证</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>源文件哈希重复数为0，图片完全重复组0、pHash近似候选1组；转账画面按业务事件去重后为7笔。pHash候选需结合transfer_id判断，同一聊天内容的多张截图可能合理近似；没有跨活动历史库。</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>pHash候选只提示画面近似，不能直接判为重复造假；本次不能排除历史活动复用。</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>人员激励-图片文件检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>真实性验证</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>文件是否重复使用</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>感知哈希（pHash）去重、跨活动文件复用检测</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>现场照片21张</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>用SHA-256查完全重复，用dHash筛查视觉相同候选，并检查同一照片是否绑定多个合同门店。</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>部分验证</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>本包完全重复组0、pHash近似候选0组；没有跨活动历史指纹库。</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>“本包未发现重复”不等于“历史活动从未使用”；跨活动复用必须接入历史SHA/pHash库。</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>堆头-照片文件检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>合规性审查</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>文件格式是否符合要求</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>文件类型、分辨率、大小是否在允许范围内</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>雨瑶人员激励参半销售数据2.xlsx；郑州雨瑶5.1-5.20人员激励活动结算单.jpg；转账截图2张</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>ZIP入口校验文件可读性、单文件大小和安全解压；Excel与图片均已成功读取。</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>部分验证</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>收到4个文件，销售Excel有效明细70行；但业务未提供允许的图片分辨率和文件大小阈值。</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>可读取不等于完全符合格式制度；需补充允许类型、最低分辨率和大小范围。</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>文件读取清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>合规性审查</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>文件格式是否符合要求</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>文件类型、分辨率、大小是否在允许范围内</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>诚成4月堆头陈列-经销商签订促销合同.pdf；2026年4月销售明细20260509164207765.xlsx；现场照片21张</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>确认PDF、XLSX、JPG均可打开；记录页数、工作表、照片分辨率和文件大小；ZIP入口执行安全大小限制。</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>部分验证</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>收到23个文件：合同PDF 1份、销售Excel 1份、JPG 21张；照片宽600–4525像素、高800–4496像素，大小123308–3431541字节。业务未提供允许阈值。</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>已证明可读性和实际尺寸，不能在没有最低分辨率/大小标准时宣称完全合规。</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>文件读取清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="96" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>合规性审查</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>费用金额是否合理</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>费用明细金额与活动预算比较，偏差超过30%标记异常</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>郑州雨瑶5.1-5.20人员激励活动结算单.jpg；雨瑶人员激励参半销售数据2.xlsx；转账截图</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>逐SKU计算数量×奖励单价，并比较结算行总额、转账总额和申报金额。</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>部分验证</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>10条SKU计算及结算行总额均为7353.00元，去重转账总额为7353.00元；申报7350.00元，差额-3.00元（0.04%）。未提供独立活动预算。</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>30%预算规则不能在没有预算表时判定；现有结果只证明结算、销售和转账之间的勾稽关系。</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>人员激励-SKU逐项</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="96" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>合规性审查</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>费用金额是否合理</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>费用明细金额与活动预算比较，偏差超过30%标记异常</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>诚成4月堆头陈列-经销商签订促销合同.pdf；申报金额</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>以本次唯一可得的合同约定金额作为合同口径，比较申报金额；另按逐店证据计算支持金额。</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>部分验证</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>合同口径20000.00元，申报20000.00元，差额0.00元（0.00%，未超过30%）；但独立活动预算表未提交。逐店证据仅支持14000.00元。</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>合同金额是现有口径，不等同于独立预算验证；若制度要求30%预算规则，需补充批准预算。</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>核销总览</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="96" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>合规性审查</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>票据信息是否完整</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>发票代码、号码、金额、日期、购销方信息完整性</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>本包未提交发票</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>盘点文件类型，未把结算单或转账截图误认作发票。</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>本案未触发</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>人员激励包包含销售Excel、结算单和转账截图，没有发票代码、号码、购销方等可核字段。</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>如公司制度规定人员激励必须附发票，应改判为证据不足并要求补交发票。</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>文件读取清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="96" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>合规性审查</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>票据信息是否完整</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>发票代码、号码、金额、日期、购销方信息完整性</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>本包未提交发票</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>盘点文件类型，未把合同、销售Excel或现场照片误认作发票。</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>本案未触发</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>没有发票代码、号码、金额、日期和购销方字段可检查。</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>如堆头付款制度要求发票，应改判为证据不足并补交发票。</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>文件读取清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="96" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>合规性审查</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>合同条款是否匹配</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>合同约定金额不低于发票总额，付款周期与开票日期一致</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>本包未提交合同；使用最终结算单及转账证明</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>检查活动期间、SKU数量、奖励单价、结算金额和转账金额；没有把结算单等同于合同。</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>本案未触发</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>可验证2026-05-01至2026-05-20的结算口径，但无合同金额、付款周期或开票日期可比。</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>如人员激励需要合同约束，应补充合同、付款周期及相应票据后再判断合同条款。</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>人员激励-SKU逐项</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="96" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>合规性审查</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>合同条款是否匹配</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>合同约定金额不低于发票总额，付款周期与开票日期一致</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>诚成4月堆头陈列-经销商签订促销合同.pdf；销售Excel；逐店照片</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>读取合同活动期、20家门店、单店1000元、陈列标准和总金额，并逐店比较照片；同时检查销售期间。</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>部分通过</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>合同20家×1000.00元=20000.00元与申报一致；逐店证据14家通过、6家补证。未提交发票，合同付款周期与开票日期无法比较。</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>合同执行条款只完成部分验证；6家补证，付款周期/开票一致性需在有发票后再检查。</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>堆头-逐店核验</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:K17"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="68" customWidth="1" min="7" max="7"/>
+    <col width="66" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="54" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>输入文件读取清单：从两个ZIP到每个原始文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>每行说明文件来自哪个ZIP、读取了哪些位置/字段、取得什么数据以及后续与谁比较；SHA-256用于固定收到后的文件身份，不等于真伪鉴定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>来源ZIP</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>ZIP SHA-256</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>压缩包内文件</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>文件角色</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>文件大小(字节)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>文件SHA-256</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>具体读取位置/字段</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>读取结果/数据量</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>后续比对工作</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="78" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SQ202604300025-HX202605260014-郑州雨瑶-人员激励.zip</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>d0f5754effbd4ad45db4d048da9dfd9c69bfebfc957cff78c7c15420c298a15f</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>（ZIP输入包本身）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>输入压缩包</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>970440</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>d0f5754effbd4ad45db4d048da9dfd9c69bfebfc957cff78c7c15420c298a15f</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>检查ZIP路径穿越、符号链接、加密、重名、文件数量、单文件大小、总展开大小和压缩比；根据文件组合与名称路由。</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>安全解压4个文件，共1045724字节；路由到人员激励子Skill。</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>冻结ZIP及所有解压文件哈希，再开始业务核验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>SQ202604300025-HX202605260014-郑州雨瑶-人员激励.zip</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>d0f5754effbd4ad45db4d048da9dfd9c69bfebfc957cff78c7c15420c298a15f</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>郑州雨瑶5.1-5.20人员激励活动结算单.jpg</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>最终结算单</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>645182</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>898a8061a91af8d681ccdb650b43a07a42b96272407ba249dd64dc53b4bbc4e6</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>按原图读取客户、活动期间、每个奖励单品、销售数量、奖励单价、行奖励金额、总数量、总奖励、实际申报、盖章和签署日期。</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>取得10条结算行；逐行映射销售Excel唯一条码，再比较数量和奖励金额。</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>逐SKU/逐门店/逐转账勾稽，详见人员激励明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>SQ202604300025-HX202605260014-郑州雨瑶-人员激励.zip</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>d0f5754effbd4ad45db4d048da9dfd9c69bfebfc957cff78c7c15420c298a15f</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>雨瑶人员激励参半销售数据2.xlsx</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>销售Excel</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>14391</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>5e1ac08e1c79fd721e2f0dcf60e09763452943309163bb2079e424b77837b5a6</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>工作表Sheet1；表头第1行；读取期间、门店、条码、商品、数量、单价和金额公式；保留原Excel行号。</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>有效明细70行、7家门店、10个SKU；按条码汇总后与最终结算单10行逐项比较。</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>逐SKU/逐门店/逐转账勾稽，详见人员激励明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>SQ202604300025-HX202605260014-郑州雨瑶-人员激励.zip</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>d0f5754effbd4ad45db4d048da9dfd9c69bfebfc957cff78c7c15420c298a15f</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>雨瑶人员激励红包图片.jpg</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>转账截图</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>194094</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>8aeda7f356dcf9123086cb55e6e60b4fc2049bfeaf784513dffcffa6f15b2529</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>读取每个金额气泡、发送/接收方向、可见收款身份、可见日期和同一转账的镜像画面关系。</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>两张截图合并为7笔去重转账；与7家门店应付金额集合比较，身份和日期另行判定。</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>逐SKU/逐门店/逐转账勾稽，详见人员激励明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="78" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>人员激励</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>SQ202604300025-HX202605260014-郑州雨瑶-人员激励.zip</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>d0f5754effbd4ad45db4d048da9dfd9c69bfebfc957cff78c7c15420c298a15f</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>雨瑶人员激励红包图片2.jpg</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>转账截图</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>192057</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>de4aa8f6d75027e207571fcf365ed5d805a350ff7622b45f29bc7d803db8c8ca</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>读取每个金额气泡、发送/接收方向、可见收款身份、可见日期和同一转账的镜像画面关系。</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>两张截图合并为7笔去重转账；与7家门店应付金额集合比较，身份和日期另行判定。</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>逐SKU/逐门店/逐转账勾稽，详见人员激励明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="78" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>（ZIP输入包本身）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>输入压缩包</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>43430687</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>检查ZIP路径穿越、符号链接、加密、重名、文件数量、单文件大小、总展开大小和压缩比；根据文件组合与名称路由。</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>安全解压23个文件，共43452756字节；路由到堆头子Skill。</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>冻结ZIP及所有解压文件哈希，再开始业务核验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/2026年4月销售明细20260509164207765.xlsx</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>销售Excel</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>30213</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>0504612568924d6686a2b752f56a5ff102fe727f901fbc631d808bd7cbfc3b48</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>工作表Sheet1；表头第1行；读取客户、业务期间、商品编码、条码、商品、数量、零售价和合计金额，并检查外部链接公式。</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>有效明细36行、数量13744、零售金额352032；文件为经销商汇总，不能替代20家门店逐店执行证据。</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/1.厚街汉邦66广场家家欣.jpg</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>491884</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2bc5b681403c0d0e05ba6394449fd73b18e211370dbdfc3b1e3166678fb33aad</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="78" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/10-1挺拇指生活超市(横沥店).jpg</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>767287</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>f12dd735b31b0e3be209767b443a5dde76af047139821839e1c380befa2f17ba</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="78" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/10-2挺拇指生活超市(横沥店).jpg</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>872772</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>1d4f8b92c71131ea2dbe09e06cff7496a82afca0ba4d7fced7ab272948670884</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="78" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/11.人人购物荟和超市.jpg</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>3431541</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>7cf34a44ba05a348179771b0c36be20c19f6a0a76fb0c72fc6742c1070011f87</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="78" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/12.三乐购物广场(森扬商业广场店).jpg</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>2609173</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>817e1b01120475a5f72ab39bce2334a3f0c5d2d7c66d02b0d02e648e70bca0e9</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="78" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/13.沙井九龙.jpg</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2762473</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>bea6157436ef7f0a45babca793b9fc67e06ac2beacd1b9eae36c44097b0e3888</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="78" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/14.润家连锁超市(美联购物中心店).jpg</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>501429</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>0589b66788746499b68c9813b97ef042c2d1a239cd70be63056d57f4a9587fe5</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="78" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/15。石岩百佳华.jpg</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>501947</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>9845f5c8c808e139ae93bf4a163372cf5e54e7aeb39a8dfbfa1d0aa47e5dfca8</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="78" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/16.田心金正和.jpg</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>762202</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>f00f97dc46a52568db5b292f7edb26bedfbc0d6f786e746acea6a56940a7c500</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="78" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/17·荟和超市(莹展荟店).jpg</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>420260</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>c6a9ac8b3b620adf996334ec432e725c45b4e302c481354caa4959a97c6f1ef1</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="78" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/18.三乐购物广场(坦洲店).jpg</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>511770</v>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>61f0c8113bfbfafd9cc02a2ae69881cb8cc456e911c32c78ba618ab3467153fe</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="78" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/19.福源大康惠.jpg</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>760801</v>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>a83b7852588f47ff9fc8c43791eab025aa930eb7efa97d4da13cd54024be754c</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="78" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/2.松岗百佳华.jpg</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>2775745</v>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>12b86e89b2996c4ee22ce55cfa65249237f10c2651963f0a74d6748f6fbdf29f</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="78" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/20.好多宝精选超市(龙眼市场店).jpg</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>380438</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>a2bc6e9f7833a6b2dace149843649c6c2a6b5988e04def5a9bc64d4b2b8740fc</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="78" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/3.公明百佳华.jpg</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>676711</v>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>334f7fe95b8f70a59cf89c0e2b65a47ba1a19c70d8b1695a51ecd59bdce07463</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="78" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/4.新桥百佳华.jpg</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>123308</v>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>df7c36d02303fc3b8df13e63888d0dcfed56860ca91d2a86501f67168d32c3ff</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="78" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/5.华都超市(东坑大道北店).jpg</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>439863</v>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>61e7f18669fe68e0686638d9bf53e6e488e8ce9ccb78192cdb6647915337dad0</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="78" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/6.东浦金正和.jpg</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1084548</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>5443f87d47fe6646e5da357f0e53a41c8934f58255619fe749eae9b7ad9596a0</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="78" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/7.宝安优城店.jpg</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>434133</v>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>80ff9c92a5eb1b780e9b0002a5d99c5239d71f592406992133c1e49e77e5834f</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="78" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/8.虎门赤岗家家欣.jpg</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>129411</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>a397af48c29cc108f54a66ac21d7aec414e79f20838ee3bb2e4851619d1f9e0a</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="78" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/堆头照片/9.花都宜多.jpg</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>现场陈列照片</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>830839</v>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>37a3bb4647855bff6147f370f02897142fb739c3b1f015546c9701327ca79c87</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>按原始分辨率读取画面日期、地点/门店水印、陈列范围和清晰度；同时记录SHA-256、pHash、dHash、尺寸、EXIF时间和GPS。</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>与合同门店逐店绑定；共21张照片支持14家通过、6家补证。</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="78" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>堆头</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】.zip</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>21216fbbf454cc0d2c59f1a55222d9e5d5b4887cccc3282a920251165d3af97a</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>核销资料-诚成26年4月【堆头20家】/诚成4月堆头陈列-经销商签订促销合同.pdf</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>促销合同</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>22154008</v>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>15ac05c881cda510b1d24743a2ae7ef7e19e5e78946b4407e6e57200cbb6a75a</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>逐页读取客户、活动起止日、陈列标准、单店费用、申报金额、盖章及完整编号门店清单。</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>合同4页、20家门店、单店1000元；作为逐店照片核验基准。</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>逐合同门店比较日期、地点、陈列和重复情况，详见堆头明细页。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J32"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6524,7 +10060,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>单店费用仅在照片、期间、门店、陈列和重复检查全部通过时计入支持金额。</t>
@@ -6650,12 +10186,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>补证</t>
         </is>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <f>IF(K4="通过",1000,0)</f>
         <v/>
       </c>
@@ -6717,12 +10253,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <f>IF(K5="通过",1000,0)</f>
         <v/>
       </c>
@@ -6784,12 +10320,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <f>IF(K6="通过",1000,0)</f>
         <v/>
       </c>
@@ -6851,12 +10387,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <f>IF(K7="通过",1000,0)</f>
         <v/>
       </c>
@@ -6918,12 +10454,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K8" s="13" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <f>IF(K8="通过",1000,0)</f>
         <v/>
       </c>
@@ -6977,12 +10513,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>补证</t>
         </is>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <f>IF(K9="通过",1000,0)</f>
         <v/>
       </c>
@@ -7044,12 +10580,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K10" s="13" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <f>IF(K10="通过",1000,0)</f>
         <v/>
       </c>
@@ -7111,12 +10647,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <f>IF(K11="通过",1000,0)</f>
         <v/>
       </c>
@@ -7178,12 +10714,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K12" s="13" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <f>IF(K12="通过",1000,0)</f>
         <v/>
       </c>
@@ -7245,12 +10781,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
         <is>
           <t>补证</t>
         </is>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <f>IF(K13="通过",1000,0)</f>
         <v/>
       </c>
@@ -7312,12 +10848,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>补证</t>
         </is>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <f>IF(K14="通过",1000,0)</f>
         <v/>
       </c>
@@ -7379,12 +10915,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="5">
         <f>IF(K15="通过",1000,0)</f>
         <v/>
       </c>
@@ -7446,12 +10982,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K16" s="13" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="5">
         <f>IF(K16="通过",1000,0)</f>
         <v/>
       </c>
@@ -7513,12 +11049,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>补证</t>
         </is>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="5">
         <f>IF(K17="通过",1000,0)</f>
         <v/>
       </c>
@@ -7580,12 +11116,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>补证</t>
         </is>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <f>IF(K18="通过",1000,0)</f>
         <v/>
       </c>
@@ -7647,12 +11183,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K19" s="13" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <f>IF(K19="通过",1000,0)</f>
         <v/>
       </c>
@@ -7714,12 +11250,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K20" s="13" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="5">
         <f>IF(K20="通过",1000,0)</f>
         <v/>
       </c>
@@ -7781,12 +11317,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="K21" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="5">
         <f>IF(K21="通过",1000,0)</f>
         <v/>
       </c>
@@ -7848,12 +11384,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K22" s="13" t="inlineStr">
+      <c r="K22" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="5">
         <f>IF(K22="通过",1000,0)</f>
         <v/>
       </c>
@@ -7915,12 +11451,12 @@
           <t>未发现</t>
         </is>
       </c>
-      <c r="K23" s="13" t="inlineStr">
+      <c r="K23" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="5">
         <f>IF(K23="通过",1000,0)</f>
         <v/>
       </c>
@@ -7971,7 +11507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7997,7 +11533,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>经销商汇总销售可证明活动期总体销售，但不能替代20家合同门店的逐店执行证据。</t>
@@ -9495,6 +13031,1069 @@
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>堆头核销：照片文件哈希与原始元数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256用于完全重复；pHash用于近似重复候选，dHash作为快速辅助指纹；EXIF/GPS缺失和跨活动历史库未接入均需保留风险。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>文件名</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>尺寸</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>文件大小</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>SHA-256</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>pHash</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>dHash</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>EXIF时间</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>绑定门店</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>1.厚街汉邦66广场家家欣.jpg</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>1279×1706</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>491884</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>2bc5b681403c0d0e05ba6394449fd73b18e211370dbdfc3b1e3166678fb33aad</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>bc40623f5dbacec0</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>d00713d3935a4615</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>66广场家家欣</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>10-1挺拇指生活超市(横沥店).jpg</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>1279×1706</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>767287</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>f12dd735b31b0e3be209767b443a5dde76af047139821839e1c380befa2f17ba</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>db04a4716159b5bd</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>6f67e7f77db14996</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>挺拇指生活超市（横沥店）</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>10-2挺拇指生活超市(横沥店).jpg</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>1279×1706</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>872772</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1d4f8b92c71131ea2dbe09e06cff7496a82afca0ba4d7fced7ab272948670884</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>8ad1fd2beb28f404</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>2b295955d4c6f43d</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>挺拇指生活超市（横沥店）</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>11.人人购物荟和超市.jpg</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>4525×4496</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>3431541</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>7cf34a44ba05a348179771b0c36be20c19f6a0a76fb0c72fc6742c1070011f87</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>df42b870745ec23c</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>93939994d070786d</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>人人购物广场荟和二店</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>12.三乐购物广场(森扬商业广场店).jpg</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>3028×4032</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>2609173</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>817e1b01120475a5f72ab39bce2334a3f0c5d2d7c66d02b0d02e648e70bca0e9</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>854b6c27e570735c</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>92b254949870783c</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>三乐购物广场（森扬商业广场店）</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>13.沙井九龙.jpg</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>4000×3003</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>2762473</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>bea6157436ef7f0a45babca793b9fc67e06ac2beacd1b9eae36c44097b0e3888</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>8ef4e07ec22cd664</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>f031717971facaca</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>沙井九龙</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>14.润家连锁超市(美联购物中心店).jpg</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>1280×1706</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>501429</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>0589b66788746499b68c9813b97ef042c2d1a239cd70be63056d57f4a9587fe5</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>aecc9d1341633373</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>5959455c59571389</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>润家连锁超市（美联购物中心店）</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>15。石岩百佳华.jpg</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>1279×1706</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>501947</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>9845f5c8c808e139ae93bf4a163372cf5e54e7aeb39a8dfbfa1d0aa47e5dfca8</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>d142a7f456b03e2b</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>8186e2f0f070e4ee</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>百佳华（石岩店）</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>16.田心金正和.jpg</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1279×1706</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>762202</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>f00f97dc46a52568db5b292f7edb26bedfbc0d6f786e746acea6a56940a7c500</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>eb89b563d205b296</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>cf892d6f5927b134</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>田心金正和</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>17·荟和超市(莹展荟店).jpg</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>1080×1920</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>420260</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>c6a9ac8b3b620adf996334ec432e725c45b4e302c481354caa4959a97c6f1ef1</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>c0357e5c8cec3574</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>0c32f4f0389eecaa</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>荟和超市（莹展荟店）</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>18.三乐购物广场(坦洲店).jpg</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>1281×1706</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>511770</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>61f0c8113bfbfafd9cc02a2ae69881cb8cc456e911c32c78ba618ab3467153fe</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>ff181159c160e0ff</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>a3eb23bb1f3b61e7</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>三乐购物广场（坦洲店）</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>19.福源大康惠.jpg</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>1279×1706</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>760801</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>a83b7852588f47ff9fc8c43791eab025aa930eb7efa97d4da13cd54024be754c</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>944b3b3cb4a64e65</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>c38712d6c6f8b683</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>大康惠福源商业广场</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2.松岗百佳华.jpg</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>3024×3759</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>2775745</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>12b86e89b2996c4ee22ce55cfa65249237f10c2651963f0a74d6748f6fbdf29f</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>d45ed0c3d0cf9847</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>e6fcd3fadbd3d3f6</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>百佳华松岗店</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>20.好多宝精选超市(龙眼市场店).jpg</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>1200×1600</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>380438</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>a2bc6e9f7833a6b2dace149843649c6c2a6b5988e04def5a9bc64d4b2b8740fc</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>d58198ddeb4063e3</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>dcebad3db48cd0b3</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>好多宝精选超市（龙眼市场店）</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>3.公明百佳华.jpg</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>1279×1706</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>676711</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>334f7fe95b8f70a59cf89c0e2b65a47ba1a19c70d8b1695a51ecd59bdce07463</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>d909f0b55d483c73</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>d66f8ba5303236b6</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>百佳华百货（公明店）</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>4.新桥百佳华.jpg</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>600×800</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>123308</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>df7c36d02303fc3b8df13e63888d0dcfed56860ca91d2a86501f67168d32c3ff</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>d21e05732f4ee5c4</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>98fe676761d2e2c1</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>百佳华佳漾汇（新桥店）</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>5.华都超市(东坑大道北店).jpg</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>1081×1440</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>439863</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>61e7f18669fe68e0686638d9bf53e6e488e8ce9ccb78192cdb6647915337dad0</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>bb17807f857c84c9</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>222b277549a9aded</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>华都超市（东坑大道北店）</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>6.东浦金正和.jpg</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>1080×1920</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1084548</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>5443f87d47fe6646e5da357f0e53a41c8934f58255619fe749eae9b7ad9596a0</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>dfc1434a3552174f</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>13636953d3f07070</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>金大福（东浦金正和总店）</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>7.宝安优城店.jpg</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>1081×1440</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>434133</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>80ff9c92a5eb1b780e9b0002a5d99c5239d71f592406992133c1e49e77e5834f</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>d04ea67a36654e71</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>c6866ee6fef8e8e9</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>古原千禧（U·ONE 优城店）</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>8.虎门赤岗家家欣.jpg</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>600×800</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>129411</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>a397af48c29cc108f54a66ac21d7aec414e79f20838ee3bb2e4851619d1f9e0a</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>8d45457f6421a5bd</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>1a232703a29cf0b4</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>虎门家家欣</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>9.花都宜多.jpg</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>1279×1706</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>830839</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>37a3bb4647855bff6147f370f02897142fb739c3b1f015546c9701327ca79c87</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>c413a95f3c3c3173</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>163bb9fb5aecf8d4</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>花都宜多</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>已绑定</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J24"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9506,947 +14105,346 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="68" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>堆头核销：照片文件哈希与原始元数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
+          <t>SQ202603300076-HX202606040013-核销资料-诚成26年4月【堆头20家】：异常与补证清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SHA-256用于完全重复检测，dHash用于快速识别视觉相同候选；EXIF/GPS缺失需在风险中保留。</t>
+          <t>高风险影响数量/金额或核心证据；中风险表示口径、身份或真实性证据仍需说明。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>文件名</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>尺寸</t>
+          <t>等级</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>文件大小</t>
+          <t>异常代码</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>SHA-256</t>
+          <t>发现</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>dHash</t>
+          <t>影响</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>EXIF时间</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>GPS</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>绑定门店</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
+          <t>补证/处理建议</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>1.厚街汉邦66广场家家欣.jpg</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>1279×1706</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>491884</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>2bc5b681403c0d0e05ba6394449fd73b18e211370dbdfc3b1e3166678fb33aad</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>d00713d3935a4615</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>66广场家家欣</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
+      <c r="A4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>合同第1家“66广场家家欣”未通过：门店未匹配。
+来源：核销资料-诚成26年4月【堆头20家】/堆头照片/1.厚街汉邦66广场家家欣.jpg</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>暂不支持该店1000.00元费用。</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>补充“66广场家家欣”与“厚街镇汉邦广场”的地址/入驻关系证明，或提供同日带完整门店名称与地点水印的现场照片。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>10-1挺拇指生活超市(横沥店).jpg</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>1279×1706</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>767287</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>f12dd735b31b0e3be209767b443a5dde76af047139821839e1c380befa2f17ba</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>6f67e7f77db14996</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>挺拇指生活超市（横沥店）</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
+      <c r="A5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>合同第6家“金大福（东浦金正和总店）”未通过：期间未通过、门店未匹配、陈列标准未通过。
+来源：核销资料-诚成26年4月【堆头20家】/堆头照片/6.东浦金正和.jpg</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>暂不支持该店1000.00元费用。</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>补充活动期内带可见日期、完整门店名称/地点水印的现场全景原图。；补充能清楚证明1平方米占地或至少4纵陈列的宽角度照片/尺寸标识。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>10-2挺拇指生活超市(横沥店).jpg</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>1279×1706</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>872772</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1d4f8b92c71131ea2dbe09e06cff7496a82afca0ba4d7fced7ab272948670884</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2b295955d4c6f43d</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>挺拇指生活超市（横沥店）</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>合同第10家“挺拇指生活超市（横沥店）”未通过：门店未匹配。
+来源：核销资料-诚成26年4月【堆头20家】/堆头照片/10-1挺拇指生活超市(横沥店).jpg、核销资料-诚成26年4月【堆头20家】/堆头照片/10-2挺拇指生活超市(横沥店).jpg</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>暂不支持该店1000.00元费用。</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>补充“挺拇指生活超市(横沥店)”位于或更名自“南铭购物乐园”的正式地址/门店映射，或提供带合同门店名称水印的现场照片。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>11.人人购物荟和超市.jpg</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>4525×4496</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>3431541</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>7cf34a44ba05a348179771b0c36be20c19f6a0a76fb0c72fc6742c1070011f87</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>93939994d070786d</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>人人购物广场荟和二店</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
+      <c r="A7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>合同第11家“人人购物广场荟和二店”未通过：门店未匹配。
+来源：核销资料-诚成26年4月【堆头20家】/堆头照片/11.人人购物荟和超市.jpg</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>暂不支持该店1000.00元费用。</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>补充“荟和二店”与“人人购物同乐店”的门店编码、地址或更名证明，或提供合同门店对应照片。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>12.三乐购物广场(森扬商业广场店).jpg</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>3028×4032</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>2609173</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>817e1b01120475a5f72ab39bce2334a3f0c5d2d7c66d02b0d02e648e70bca0e9</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>92b254949870783c</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>三乐购物广场（森扬商业广场店）</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
+      <c r="A8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>合同第14家“润家连锁超市（美联购物中心店）”未通过：门店未匹配。
+来源：核销资料-诚成26年4月【堆头20家】/堆头照片/14.润家连锁超市(美联购物中心店).jpg</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>暂不支持该店1000.00元费用。</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>提供“深圳紫云快捷宾馆”定位与润家连锁超市(美联购物中心店)同址的权威地址证明，或重拍带合同门店地点水印的现场照片。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>13.沙井九龙.jpg</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>4000×3003</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>2762473</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>bea6157436ef7f0a45babca793b9fc67e06ac2beacd1b9eae36c44097b0e3888</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>f031717971facaca</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>沙井九龙</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
+      <c r="A9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>STORE_DISPLAY_EVIDENCE_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>合同第15家“百佳华（石岩店）”未通过：门店未匹配。
+来源：核销资料-诚成26年4月【堆头20家】/堆头照片/15。石岩百佳华.jpg</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>暂不支持该店1000.00元费用。</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>补充百佳华(石岩店)与“佳华豪苑”的权威地址/入驻关系证明，或提供带完整门店名地点水印的清晰原图。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>14.润家连锁超市(美联购物中心店).jpg</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>1280×1706</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>501429</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>0589b66788746499b68c9813b97ef042c2d1a239cd70be63056d57f4a9587fe5</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>5959455c59571389</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>润家连锁超市（美联购物中心店）</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
+      <c r="A10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>PHOTO_ORIGINAL_METADATA_ABSENT</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>照片缺少可用的EXIF拍摄时间或GPS，主要依赖画面水印。</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>无法从原始文件元数据独立验证拍摄时空。</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>保留原始拍摄文件，或补充平台定位/签到记录。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>15。石岩百佳华.jpg</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>1279×1706</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>501947</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>9845f5c8c808e139ae93bf4a163372cf5e54e7aeb39a8dfbfa1d0aa47e5dfca8</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>8186e2f0f070e4ee</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>百佳华（石岩店）</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
+      <c r="A11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>SALES_DATA_NOT_STORE_LEVEL</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>销售Excel为经销商汇总，不能拆分到合同中的各门店。
+来源：C:\Users\EDY\Desktop\新建文件夹\offline-activity-audit\input\.prepared\20260814-live-003\sources\promotional_display\核销资料-诚成26年4月【堆头20家】\2026年4月销售明细20260509164207765.xlsx</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>销售数据只能证明活动期总体销售，不能独立证明逐店执行。</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>如政策要求逐店销售佐证，补交门店级POS或出库明细。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>16.田心金正和.jpg</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>1279×1706</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>762202</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>f00f97dc46a52568db5b292f7edb26bedfbc0d6f786e746acea6a56940a7c500</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>cf892d6f5927b134</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>田心金正和</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>17·荟和超市(莹展荟店).jpg</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>1080×1920</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>420260</v>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>c6a9ac8b3b620adf996334ec432e725c45b4e302c481354caa4959a97c6f1ef1</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>0c32f4f0389eecaa</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>荟和超市（莹展荟店）</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>18.三乐购物广场(坦洲店).jpg</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>1281×1706</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>511770</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>61f0c8113bfbfafd9cc02a2ae69881cb8cc456e911c32c78ba618ab3467153fe</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>a3eb23bb1f3b61e7</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>三乐购物广场（坦洲店）</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>19.福源大康惠.jpg</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>1279×1706</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>760801</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>a83b7852588f47ff9fc8c43791eab025aa930eb7efa97d4da13cd54024be754c</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>c38712d6c6f8b683</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>大康惠福源商业广场</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>2.松岗百佳华.jpg</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>3024×3759</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>2775745</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>12b86e89b2996c4ee22ce55cfa65249237f10c2651963f0a74d6748f6fbdf29f</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>e6fcd3fadbd3d3f6</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>百佳华松岗店</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>20.好多宝精选超市(龙眼市场店).jpg</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>1200×1600</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>380438</v>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>a2bc6e9f7833a6b2dace149843649c6c2a6b5988e04def5a9bc64d4b2b8740fc</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>dcebad3db48cd0b3</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>好多宝精选超市（龙眼市场店）</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>3.公明百佳华.jpg</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>1279×1706</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>676711</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>334f7fe95b8f70a59cf89c0e2b65a47ba1a19c70d8b1695a51ecd59bdce07463</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>d66f8ba5303236b6</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>百佳华百货（公明店）</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>4.新桥百佳华.jpg</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>600×800</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>123308</v>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>df7c36d02303fc3b8df13e63888d0dcfed56860ca91d2a86501f67168d32c3ff</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>98fe676761d2e2c1</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>百佳华佳漾汇（新桥店）</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>5.华都超市(东坑大道北店).jpg</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>1081×1440</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>439863</v>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>61e7f18669fe68e0686638d9bf53e6e488e8ce9ccb78192cdb6647915337dad0</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>222b277549a9aded</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>华都超市（东坑大道北店）</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>6.东浦金正和.jpg</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>1080×1920</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1084548</v>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>5443f87d47fe6646e5da357f0e53a41c8934f58255619fe749eae9b7ad9596a0</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>13636953d3f07070</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>金大福（东浦金正和总店）</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>7.宝安优城店.jpg</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>1081×1440</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>434133</v>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>80ff9c92a5eb1b780e9b0002a5d99c5239d71f592406992133c1e49e77e5834f</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>c6866ee6fef8e8e9</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>古原千禧（U·ONE 优城店）</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>8.虎门赤岗家家欣.jpg</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>600×800</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>129411</v>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>a397af48c29cc108f54a66ac21d7aec414e79f20838ee3bb2e4851619d1f9e0a</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>1a232703a29cf0b4</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>虎门家家欣</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>9.花都宜多.jpg</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>1279×1706</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>830839</v>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>37a3bb4647855bff6147f370f02897142fb739c3b1f015546c9701327ca79c87</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>163bb9fb5aecf8d4</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>花都宜多</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>已绑定</t>
+      <c r="A12" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>SALES_EXCEL_EXTERNAL_LINKS</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>销售Excel有36个公式引用缺失的外部工作簿。
+来源：H10,H11,H16,H17,H21,H22,H27,H30,H31,H33,H34,H9,L11,L13,L14,L15,L16,L17,L2,L20</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>部分单位或零售价无法在当前文件内独立重算。</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>补交被引用主数据或将外链转为可追溯静态值。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I24"/>
+  <autoFilter ref="A3:F12"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
